--- a/Results/Hydrogen/hydrogen climate change remind breakdown results.xlsx
+++ b/Results/Hydrogen/hydrogen climate change remind breakdown results.xlsx
@@ -1121,37 +1121,37 @@
         <v>10.39850986057385</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01855441535449745</v>
+        <v>0.01855441535449746</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04168000631594184</v>
+        <v>0.04168000631594185</v>
       </c>
       <c r="G2" t="n">
-        <v>3.711107245476235e-05</v>
+        <v>3.711107245476231e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001019079028989823</v>
+        <v>0.001019079028989828</v>
       </c>
       <c r="I2" t="n">
         <v>0.000207683396662165</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001588092258278459</v>
+        <v>0.001588092258278462</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003688580575341322</v>
+        <v>0.003688580575341319</v>
       </c>
       <c r="L2" t="n">
         <v>3.152046796287712e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>9.635959780726154e-05</v>
+        <v>9.635959780726153e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003848856747473808</v>
+        <v>0.003848856747473811</v>
       </c>
       <c r="O2" t="n">
-        <v>3.08197596435446e-05</v>
+        <v>3.081975964354437e-05</v>
       </c>
       <c r="P2" t="n">
         <v>4.757221769782728e-07</v>
@@ -1160,43 +1160,43 @@
         <v>5.807906064559163e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.542665813998698e-07</v>
+        <v>5.542665813998705e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.194520047534008e-06</v>
+        <v>2.194520047534009e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0006866744914405374</v>
+        <v>0.0006866744914405375</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002356904167017029</v>
+        <v>0.002356904167017028</v>
       </c>
       <c r="V2" t="n">
         <v>0.004518609097640749</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002421297367460325</v>
+        <v>0.000242129736746033</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.502877407733335</v>
+        <v>-0.502877407733336</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.650832358096439e-16</v>
+        <v>2.65083235809644e-16</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004401507007203523</v>
+        <v>0.004401507007203522</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01412900872854348</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001793309948872447</v>
+        <v>0.001793309948872448</v>
       </c>
       <c r="AC2" t="n">
         <v>0.001933164570469227</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3216295800154748</v>
+        <v>0.321629580015475</v>
       </c>
       <c r="AE2" t="n">
         <v>0.0003633475813021559</v>
@@ -1214,7 +1214,7 @@
         <v>0.003052998564529259</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5.041700284247387e-06</v>
+        <v>5.041700284247386e-06</v>
       </c>
       <c r="AK2" t="n">
         <v>0.0005337188923224738</v>
@@ -1226,19 +1226,19 @@
         <v>0.1122844533562152</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.006528094753722251</v>
+        <v>0.006528094753722254</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.002475098592544163</v>
+        <v>0.002475098592544162</v>
       </c>
       <c r="AP2" t="n">
         <v>0.003440150834454836</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.645803868702903e-14</v>
+        <v>4.645803868702902e-14</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.003164181037793459</v>
+        <v>0.00316418103779346</v>
       </c>
       <c r="AS2" t="n">
         <v>1.127067265209926e-06</v>
@@ -1253,31 +1253,31 @@
         <v>0.0001833054983925689</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.001851352816397392</v>
+        <v>0.001851352816397391</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0003251191089579982</v>
+        <v>0.0003251191089579981</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0005229301886839402</v>
+        <v>0.0005229301886839404</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.002958612288762146</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0006035094160578593</v>
+        <v>0.0006035094160578592</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.497165573690107e-05</v>
+        <v>5.497165573690106e-05</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.824516818447474e-05</v>
+        <v>5.824516818447473e-05</v>
       </c>
       <c r="BD2" t="n">
         <v>1.032953687323069e-06</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.2229001810853539</v>
+        <v>0.222900181085354</v>
       </c>
       <c r="BF2" t="n">
         <v>0.007081989199254837</v>
@@ -1286,10 +1286,10 @@
         <v>1.581067622474389e-05</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.05621905429188433</v>
+        <v>0.05621905429188431</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0004138785633943315</v>
+        <v>0.0004138785633943313</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.0003287747270972844</v>
@@ -1304,7 +1304,7 @@
         <v>0.0001151834378325539</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.972276825693561e-06</v>
+        <v>5.97227682569356e-06</v>
       </c>
       <c r="BO2" t="n">
         <v>0.001669965200210168</v>
@@ -1316,22 +1316,22 @@
         <v>0.001327913189238496</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0008566708179296424</v>
+        <v>0.0008566708179296423</v>
       </c>
       <c r="BS2" t="n">
         <v>0.01014747228838597</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.007081989199254836</v>
+        <v>0.007081989199254839</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.06404521635802632</v>
+        <v>0.06404521635802629</v>
       </c>
       <c r="BV2" t="n">
         <v>6.511551774512961e-05</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.4427830934765243</v>
+        <v>0.4427830934765242</v>
       </c>
       <c r="BX2" t="n">
         <v>4.129073325730765e-07</v>
@@ -1340,13 +1340,13 @@
         <v>0.0002373266258004819</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.04002427663174938</v>
+        <v>0.04002427663174935</v>
       </c>
       <c r="CA2" t="n">
         <v>0.0002346323714981756</v>
       </c>
       <c r="CB2" t="n">
-        <v>9.926987758330785e-05</v>
+        <v>9.926987758330784e-05</v>
       </c>
       <c r="CC2" t="n">
         <v>0.0004506136434344263</v>
@@ -1355,25 +1355,25 @@
         <v>0.0002556796782422493</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0700839674785968</v>
+        <v>0.07008396747859683</v>
       </c>
       <c r="CF2" t="n">
         <v>0.0006120850411371574</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.01797018388750413</v>
+        <v>0.01797018388750412</v>
       </c>
       <c r="CH2" t="n">
         <v>0.0002387905456177171</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0004074369778146782</v>
+        <v>0.0004074369778146783</v>
       </c>
       <c r="CJ2" t="n">
         <v>5.659116803028843e-05</v>
       </c>
       <c r="CK2" t="n">
-        <v>4.240860273808232e-05</v>
+        <v>4.240860273808231e-05</v>
       </c>
       <c r="CL2" t="n">
         <v>0.000469907873773413</v>
@@ -1382,7 +1382,7 @@
         <v>0.003111755522032076</v>
       </c>
       <c r="CN2" t="n">
-        <v>6.019279572331536e-05</v>
+        <v>6.019279572331534e-05</v>
       </c>
       <c r="CO2" t="n">
         <v>0.002074057644229793</v>
@@ -1391,7 +1391,7 @@
         <v>0.0003017766521092619</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.000914014343786339</v>
+        <v>0.0009140143437863389</v>
       </c>
       <c r="CR2" t="n">
         <v>1.13286332104025e-05</v>
@@ -1400,16 +1400,16 @@
         <v>0.0002641148801772878</v>
       </c>
       <c r="CT2" t="n">
-        <v>4.619295618666611e-14</v>
+        <v>4.619295618666612e-14</v>
       </c>
       <c r="CU2" t="n">
-        <v>9.572201040249797e-05</v>
+        <v>9.572201040249798e-05</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0007301020483061387</v>
+        <v>0.000730102048306139</v>
       </c>
       <c r="CW2" t="n">
-        <v>5.924027217432682e-05</v>
+        <v>5.924027217432683e-05</v>
       </c>
       <c r="CX2" t="n">
         <v>1.020673095106014e-07</v>
@@ -1421,7 +1421,7 @@
         <v>2.287544018061451e-13</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.911731869361039e-13</v>
+        <v>1.911731869361038e-13</v>
       </c>
       <c r="DB2" t="n">
         <v>9.381438381870665e-14</v>
@@ -1430,13 +1430,13 @@
         <v>2.058172647998602e-13</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.125961816993104e-13</v>
+        <v>2.125961816993105e-13</v>
       </c>
       <c r="DE2" t="n">
         <v>3.31222593141384e-22</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.416636920073547e-22</v>
+        <v>2.416636920073549e-22</v>
       </c>
       <c r="DG2" t="n">
         <v>2.034132834844202e-22</v>
@@ -1445,7 +1445,7 @@
         <v>1.057887138821382e-22</v>
       </c>
       <c r="DI2" t="n">
-        <v>2.186145732648607e-22</v>
+        <v>2.186145732648605e-22</v>
       </c>
       <c r="DJ2" t="n">
         <v>2.254305791815764e-22</v>
@@ -1457,13 +1457,13 @@
         <v>2.912622876088525e-13</v>
       </c>
       <c r="DM2" t="n">
-        <v>3.014691267692351e-13</v>
+        <v>3.01469126769235e-13</v>
       </c>
       <c r="DN2" t="n">
         <v>1.306742846830264e-13</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.452418384064685e-13</v>
+        <v>3.452418384064684e-13</v>
       </c>
       <c r="DP2" t="n">
         <v>2.909094420103712e-13</v>
@@ -1472,7 +1472,7 @@
         <v>3.231067754089778e-13</v>
       </c>
       <c r="DR2" t="n">
-        <v>2.590749281063806e-13</v>
+        <v>2.590749281063805e-13</v>
       </c>
       <c r="DS2" t="n">
         <v>2.416775384841513e-13</v>
@@ -1493,10 +1493,10 @@
         <v>2.408709669074311e-13</v>
       </c>
       <c r="DY2" t="n">
-        <v>3.538934994565757e-13</v>
+        <v>3.538934994565758e-13</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.64004864787876e-13</v>
+        <v>2.640048647878762e-13</v>
       </c>
       <c r="EA2" t="n">
         <v>2.254965518737896e-13</v>
@@ -1508,10 +1508,10 @@
         <v>6.081593097341452e-12</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.4460420952297832</v>
+        <v>0.4460420952297834</v>
       </c>
       <c r="EE2" t="n">
-        <v>8.925190069011542</v>
+        <v>8.925190069011544</v>
       </c>
     </row>
     <row r="3">
@@ -1532,88 +1532,88 @@
         <v>10.54347538417608</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01577062854574099</v>
+        <v>0.015770628545741</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03526619308977442</v>
+        <v>0.03526619308977446</v>
       </c>
       <c r="G3" t="n">
         <v>3.618152429568153e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009794906194032099</v>
+        <v>0.0009794906194032047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002001284746939458</v>
+        <v>0.0002001284746939455</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001332464554329938</v>
+        <v>0.00133246455432994</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003379392170279086</v>
+        <v>0.003379392170279085</v>
       </c>
       <c r="L3" t="n">
-        <v>3.07297472560523e-05</v>
+        <v>3.072974725605233e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>7.989072484803267e-05</v>
+        <v>7.989072484803273e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003718494301112276</v>
+        <v>0.003718494301112272</v>
       </c>
       <c r="O3" t="n">
-        <v>2.931204071409317e-05</v>
+        <v>2.931204071409343e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.723093556881964e-07</v>
+        <v>4.723093556881965e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.755013933489767e-05</v>
+        <v>5.755013933489771e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.400180247227017e-07</v>
+        <v>5.40018024722704e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.933186996262399e-06</v>
+        <v>1.933186996262402e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005989989047740115</v>
+        <v>0.0005989989047740105</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002053528908786063</v>
+        <v>0.002053528908788218</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004514590744794408</v>
+        <v>0.00451459074479441</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002175691359668182</v>
+        <v>0.0002175691359668187</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3299818522707373</v>
+        <v>-0.3299818522707372</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.457220429294471e-16</v>
+        <v>2.45722042929447e-16</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004374812925473722</v>
+        <v>0.004374812925473724</v>
       </c>
       <c r="AA3" t="n">
         <v>0.01404209016407831</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001751057636967104</v>
+        <v>0.001751057636967105</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.001921157535597651</v>
+        <v>0.001921157535597652</v>
       </c>
       <c r="AD3" t="n">
         <v>0.3176370843388968</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0003609930045544057</v>
+        <v>0.0003609930045544056</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0009960315510656598</v>
+        <v>0.00099603155106566</v>
       </c>
       <c r="AG3" t="n">
         <v>4.17547808360314e-07</v>
@@ -1622,13 +1622,13 @@
         <v>0.0001089405088693315</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.003034569895005342</v>
+        <v>0.003034569895005343</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5.011123584216102e-06</v>
+        <v>5.011123584216103e-06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.000521479321130394</v>
+        <v>0.0005214793211303941</v>
       </c>
       <c r="AL3" t="n">
         <v>2.037376546291781e-05</v>
@@ -1637,16 +1637,16 @@
         <v>0.1122844533562152</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.006367549289292218</v>
+        <v>0.006367549289292216</v>
       </c>
       <c r="AO3" t="n">
         <v>0.002459347037923458</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.003421473061773509</v>
+        <v>0.003421473061773508</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.170891329097112e-14</v>
+        <v>4.170891329097117e-14</v>
       </c>
       <c r="AR3" t="n">
         <v>0.003141447883549494</v>
@@ -1658,7 +1658,7 @@
         <v>2.028280096245654e-06</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.57232636451012e-06</v>
+        <v>2.572326364510121e-06</v>
       </c>
       <c r="AV3" t="n">
         <v>0.0001792545998067953</v>
@@ -1667,7 +1667,7 @@
         <v>0.001839512616772969</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0003212086186255114</v>
+        <v>0.0003212086186255111</v>
       </c>
       <c r="AY3" t="n">
         <v>0.0005082845510211072</v>
@@ -1676,19 +1676,19 @@
         <v>0.002940583941541556</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0005937506559316065</v>
+        <v>0.0005937506559316068</v>
       </c>
       <c r="BB3" t="n">
         <v>5.480157642978834e-05</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.687284935322249e-05</v>
+        <v>5.68728493532225e-05</v>
       </c>
       <c r="BD3" t="n">
         <v>1.002411583960168e-06</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.2192094820930584</v>
+        <v>0.2192094820930585</v>
       </c>
       <c r="BF3" t="n">
         <v>0.007062187021521266</v>
@@ -1700,16 +1700,16 @@
         <v>0.05537983791939562</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0004097141255927023</v>
+        <v>0.0004097141255927018</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0003278772854252623</v>
+        <v>0.0003278772854252622</v>
       </c>
       <c r="BK3" t="n">
         <v>0.01273734033029897</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0003390935590812613</v>
+        <v>0.0003390935590812614</v>
       </c>
       <c r="BM3" t="n">
         <v>0.0001126686449570384</v>
@@ -1721,40 +1721,40 @@
         <v>0.001628313659305747</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.000971382480281701</v>
+        <v>0.0009713824802817009</v>
       </c>
       <c r="BQ3" t="n">
         <v>0.001317979014847336</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0008224145157192834</v>
+        <v>0.0008224145157192837</v>
       </c>
       <c r="BS3" t="n">
         <v>0.01008679072814839</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.007062187021521266</v>
+        <v>0.007062187021521264</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.06337369575368244</v>
+        <v>0.06337369575368247</v>
       </c>
       <c r="BV3" t="n">
         <v>6.322070947477493e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.4396629934763472</v>
+        <v>0.4396629934763471</v>
       </c>
       <c r="BX3" t="n">
-        <v>4.065667223304614e-07</v>
+        <v>4.065667223304615e-07</v>
       </c>
       <c r="BY3" t="n">
         <v>0.0002290755755590689</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0394549442456292</v>
+        <v>0.03945494424562922</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0002303534550014137</v>
+        <v>0.0002303534550014136</v>
       </c>
       <c r="CB3" t="n">
         <v>9.742058894385365e-05</v>
@@ -1763,67 +1763,67 @@
         <v>0.0004388518075691081</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0002507189649792175</v>
+        <v>0.0002507189649792176</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.06914062103822102</v>
+        <v>0.069140621038221</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0006084951599938683</v>
+        <v>0.0006084951599938684</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.01767982151763505</v>
+        <v>0.01767982151763507</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0002374015631136098</v>
+        <v>0.0002374015631136099</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0004061763900090194</v>
+        <v>0.0004061763900090193</v>
       </c>
       <c r="CJ3" t="n">
         <v>5.628829435243616e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>4.154856304163587e-05</v>
+        <v>4.154856304163588e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0004536023253809443</v>
+        <v>0.0004536023253809444</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.003090911739980481</v>
+        <v>0.00309091173998048</v>
       </c>
       <c r="CN3" t="n">
-        <v>5.907279620791193e-05</v>
+        <v>5.907279620791195e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.002061175511564865</v>
+        <v>0.002061175511564866</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.0002999804216509538</v>
+        <v>0.0002999804216509539</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0008941053986821826</v>
+        <v>0.0008941053986821827</v>
       </c>
       <c r="CR3" t="n">
         <v>1.120890131538333e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0002541812720810815</v>
+        <v>0.0002541812720810816</v>
       </c>
       <c r="CT3" t="n">
-        <v>4.146319190832569e-14</v>
+        <v>4.146319190832574e-14</v>
       </c>
       <c r="CU3" t="n">
-        <v>9.394092341399788e-05</v>
+        <v>9.394092341399792e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0007211045568096149</v>
+        <v>0.0007211045568096147</v>
       </c>
       <c r="CW3" t="n">
-        <v>5.756521605210104e-05</v>
+        <v>5.756521605210106e-05</v>
       </c>
       <c r="CX3" t="n">
-        <v>9.981170712346114e-08</v>
+        <v>9.981170712346116e-08</v>
       </c>
       <c r="CY3" t="n">
         <v>3.150548790918194e-13</v>
@@ -1835,7 +1835,7 @@
         <v>1.893513624877926e-13</v>
       </c>
       <c r="DB3" t="n">
-        <v>9.231280804709395e-14</v>
+        <v>9.231280804709397e-14</v>
       </c>
       <c r="DC3" t="n">
         <v>2.032441468402357e-13</v>
@@ -1844,7 +1844,7 @@
         <v>2.096450391048427e-13</v>
       </c>
       <c r="DE3" t="n">
-        <v>3.283424735840676e-22</v>
+        <v>3.283424735840675e-22</v>
       </c>
       <c r="DF3" t="n">
         <v>2.375864538414753e-22</v>
@@ -1856,19 +1856,19 @@
         <v>1.042349211275146e-22</v>
       </c>
       <c r="DI3" t="n">
-        <v>2.159851056274986e-22</v>
+        <v>2.159851056274985e-22</v>
       </c>
       <c r="DJ3" t="n">
         <v>2.2242047847906e-22</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.093942474103481e-13</v>
+        <v>2.093942474103482e-13</v>
       </c>
       <c r="DL3" t="n">
-        <v>2.894913767312936e-13</v>
+        <v>2.894913767312935e-13</v>
       </c>
       <c r="DM3" t="n">
-        <v>2.961968560078704e-13</v>
+        <v>2.961968560078705e-13</v>
       </c>
       <c r="DN3" t="n">
         <v>1.288133595079927e-13</v>
@@ -1877,16 +1877,16 @@
         <v>3.43825530932353e-13</v>
       </c>
       <c r="DP3" t="n">
-        <v>2.878461818324805e-13</v>
+        <v>2.878461818324806e-13</v>
       </c>
       <c r="DQ3" t="n">
         <v>3.2193175682429e-13</v>
       </c>
       <c r="DR3" t="n">
-        <v>2.563942289142249e-13</v>
+        <v>2.56394228914225e-13</v>
       </c>
       <c r="DS3" t="n">
-        <v>2.404704478912838e-13</v>
+        <v>2.404704478912839e-13</v>
       </c>
       <c r="DT3" t="n">
         <v>2.346296932895724e-13</v>
@@ -1901,13 +1901,13 @@
         <v>2.44478438408416e-13</v>
       </c>
       <c r="DX3" t="n">
-        <v>2.380186153831421e-13</v>
+        <v>2.380186153831419e-13</v>
       </c>
       <c r="DY3" t="n">
         <v>3.507894396681653e-13</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.596992788987915e-13</v>
+        <v>2.596992788987913e-13</v>
       </c>
       <c r="EA3" t="n">
         <v>2.23402926812645e-13</v>
@@ -1922,7 +1922,7 @@
         <v>0.4435917337609626</v>
       </c>
       <c r="EE3" t="n">
-        <v>8.925190254742477</v>
+        <v>8.925190254742475</v>
       </c>
     </row>
     <row r="4">
@@ -1940,73 +1940,73 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.65525535066931</v>
+        <v>10.65525535066932</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01374377310886611</v>
+        <v>0.01374377310886613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03072280134403407</v>
+        <v>0.03072280134403403</v>
       </c>
       <c r="G4" t="n">
-        <v>3.558581075995067e-05</v>
+        <v>3.558581075995063e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000950504547549191</v>
+        <v>0.0009505045475491903</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001941168689060118</v>
+        <v>0.0001941168689060122</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001157182598009482</v>
+        <v>0.001157182598009476</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003209715869429784</v>
+        <v>0.00320971586942978</v>
       </c>
       <c r="L4" t="n">
-        <v>3.014914733453491e-05</v>
+        <v>3.014914733453487e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.857146497052925e-05</v>
+        <v>6.85714649705293e-05</v>
       </c>
       <c r="N4" t="n">
         <v>0.003646501527607014</v>
       </c>
       <c r="O4" t="n">
-        <v>2.814252474244337e-05</v>
+        <v>2.814252474244216e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.694387028624423e-07</v>
+        <v>4.694387028624427e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.709313004322674e-05</v>
+        <v>5.709313004322671e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>5.23403793731917e-07</v>
+        <v>5.234037937319164e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.731968031356611e-06</v>
+        <v>1.731968031356613e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0005339979872632793</v>
+        <v>0.000533997987263279</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00182974384755499</v>
+        <v>0.001829743847554899</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004505771588607392</v>
+        <v>0.004505771588607391</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000198256347159472</v>
+        <v>0.0001982563471594726</v>
       </c>
       <c r="X4" t="n">
         <v>-0.2083679750836228</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.301082495276146e-16</v>
+        <v>2.301082495276147e-16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00435914107054972</v>
+        <v>0.004359141070549721</v>
       </c>
       <c r="AA4" t="n">
         <v>0.01398977218037445</v>
@@ -2018,10 +2018,10 @@
         <v>0.001913811802456204</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3153562735136316</v>
+        <v>0.3153562735136317</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0003608596710445562</v>
+        <v>0.0003608596710445561</v>
       </c>
       <c r="AF4" t="n">
         <v>0.0009926360217963142</v>
@@ -2036,7 +2036,7 @@
         <v>0.003023841823266251</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.993172279061818e-06</v>
+        <v>4.993172279061817e-06</v>
       </c>
       <c r="AK4" t="n">
         <v>0.0005130753006419682</v>
@@ -2048,7 +2048,7 @@
         <v>0.1122844533562152</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.006297708045697177</v>
+        <v>0.006297708045697176</v>
       </c>
       <c r="AO4" t="n">
         <v>0.002449323010013335</v>
@@ -2066,7 +2066,7 @@
         <v>1.089445792216872e-06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.010391266227737e-06</v>
+        <v>2.010391266227736e-06</v>
       </c>
       <c r="AU4" t="n">
         <v>2.514873608360359e-06</v>
@@ -2075,19 +2075,19 @@
         <v>0.0001767034470313025</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001831919599536905</v>
+        <v>0.001831919599536906</v>
       </c>
       <c r="AX4" t="n">
         <v>0.000318650418242531</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0004997011183799058</v>
+        <v>0.0004997011183799056</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.002929910479348202</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0005884354105538101</v>
+        <v>0.00058843541055381</v>
       </c>
       <c r="BB4" t="n">
         <v>5.473368015857407e-05</v>
@@ -2108,7 +2108,7 @@
         <v>1.573892452478288e-05</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.05478953795333308</v>
+        <v>0.05478953795333309</v>
       </c>
       <c r="BI4" t="n">
         <v>0.0004069715399102441</v>
@@ -2126,13 +2126,13 @@
         <v>0.0001110853146683227</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.827249145282283e-06</v>
+        <v>5.827249145282282e-06</v>
       </c>
       <c r="BO4" t="n">
         <v>0.001599409849597564</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0009667717851578716</v>
+        <v>0.0009667717851578717</v>
       </c>
       <c r="BQ4" t="n">
         <v>0.001313839385998669</v>
@@ -2147,16 +2147,16 @@
         <v>0.007050208465214388</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.06298701026164619</v>
+        <v>0.06298701026164616</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.209758065282596e-05</v>
+        <v>6.209758065282598e-05</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.4413768245998037</v>
+        <v>0.4413768245998036</v>
       </c>
       <c r="BX4" t="n">
-        <v>4.026633599788295e-07</v>
+        <v>4.026633599788296e-07</v>
       </c>
       <c r="BY4" t="n">
         <v>0.0002239095290966803</v>
@@ -2168,16 +2168,16 @@
         <v>0.0002275155176401973</v>
       </c>
       <c r="CB4" t="n">
-        <v>9.617609274671987e-05</v>
+        <v>9.617609274671985e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0004306460945294443</v>
+        <v>0.0004306460945294442</v>
       </c>
       <c r="CD4" t="n">
         <v>0.0002473948000547431</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.06889598553008693</v>
+        <v>0.06889598553008691</v>
       </c>
       <c r="CF4" t="n">
         <v>0.0006065086419722269</v>
@@ -2204,13 +2204,13 @@
         <v>0.003078634684835459</v>
       </c>
       <c r="CN4" t="n">
-        <v>5.832742547931407e-05</v>
+        <v>5.832742547931406e-05</v>
       </c>
       <c r="CO4" t="n">
         <v>0.002053294406041193</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0002989614832868809</v>
+        <v>0.0002989614832868808</v>
       </c>
       <c r="CQ4" t="n">
         <v>0.0008805309174401828</v>
@@ -2222,67 +2222,67 @@
         <v>0.0002478330611766896</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.82232919547479e-14</v>
+        <v>3.822329195474787e-14</v>
       </c>
       <c r="CU4" t="n">
-        <v>9.27555924490676e-05</v>
+        <v>9.275559244906759e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0007151154480613968</v>
+        <v>0.0007151154480613972</v>
       </c>
       <c r="CW4" t="n">
         <v>5.639271738858377e-05</v>
       </c>
       <c r="CX4" t="n">
-        <v>9.839118617767155e-08</v>
+        <v>9.839118617767154e-08</v>
       </c>
       <c r="CY4" t="n">
-        <v>3.139468697780263e-13</v>
+        <v>3.139468697780264e-13</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.220130057635088e-13</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.881565418682102e-13</v>
+        <v>1.881565418682101e-13</v>
       </c>
       <c r="DB4" t="n">
-        <v>9.130014400494127e-14</v>
+        <v>9.130014400494126e-14</v>
       </c>
       <c r="DC4" t="n">
         <v>2.015480453526701e-13</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.078711637874064e-13</v>
+        <v>2.078711637874065e-13</v>
       </c>
       <c r="DE4" t="n">
-        <v>3.272127865141404e-22</v>
+        <v>3.272127865141402e-22</v>
       </c>
       <c r="DF4" t="n">
         <v>2.348287293794278e-22</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.003236280467163e-22</v>
+        <v>2.003236280467162e-22</v>
       </c>
       <c r="DH4" t="n">
-        <v>1.032007391902475e-22</v>
+        <v>1.032007391902476e-22</v>
       </c>
       <c r="DI4" t="n">
-        <v>2.1426493640446e-22</v>
+        <v>2.142649364044601e-22</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.206214180948129e-22</v>
+        <v>2.20621418094813e-22</v>
       </c>
       <c r="DK4" t="n">
         <v>2.072477638863295e-13</v>
       </c>
       <c r="DL4" t="n">
-        <v>2.885438513551076e-13</v>
+        <v>2.885438513551075e-13</v>
       </c>
       <c r="DM4" t="n">
         <v>2.936013337777768e-13</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.275423473429888e-13</v>
+        <v>1.275423473429887e-13</v>
       </c>
       <c r="DO4" t="n">
         <v>3.431344526259986e-13</v>
@@ -2309,7 +2309,7 @@
         <v>1.127805474341848e-13</v>
       </c>
       <c r="DW4" t="n">
-        <v>2.425106679936036e-13</v>
+        <v>2.425106679936037e-13</v>
       </c>
       <c r="DX4" t="n">
         <v>2.361302043093286e-13</v>
@@ -2321,7 +2321,7 @@
         <v>2.567693743558307e-13</v>
       </c>
       <c r="EA4" t="n">
-        <v>2.220207168957599e-13</v>
+        <v>2.2202071689576e-13</v>
       </c>
       <c r="EB4" t="n">
         <v>1.245903924999433e-13</v>
@@ -2354,67 +2354,67 @@
         <v>10.51303766485157</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01501160443119466</v>
+        <v>0.01501160443119468</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03414234762496613</v>
+        <v>0.03414234762496619</v>
       </c>
       <c r="G5" t="n">
-        <v>3.581479037255498e-05</v>
+        <v>3.581479037255482e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009626207539243134</v>
+        <v>0.0009626207539243145</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001974297456720539</v>
+        <v>0.000197429745672054</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001281528264248147</v>
+        <v>0.001281528264248156</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003334666052550513</v>
+        <v>0.003334666052550517</v>
       </c>
       <c r="L5" t="n">
         <v>3.036914275775102e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>7.726431197609175e-05</v>
+        <v>7.726431197609167e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003672515688834676</v>
+        <v>0.00367251568883468</v>
       </c>
       <c r="O5" t="n">
-        <v>2.761899199809431e-05</v>
+        <v>2.761899199809543e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.684579518107721e-07</v>
+        <v>4.684579518107722e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.729359103275018e-05</v>
+        <v>5.729359103275021e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>5.24526386117127e-07</v>
+        <v>5.24526386117135e-07</v>
       </c>
       <c r="S5" t="n">
         <v>1.785236941391481e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0005809248794188004</v>
+        <v>0.0005809248794188007</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001996762229094881</v>
+        <v>0.001996762229094879</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004506676414325724</v>
+        <v>0.004506676414325722</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000209941761130004</v>
+        <v>0.0002099417611300026</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3150495938427558</v>
+        <v>-0.3150495938427554</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.156220662648605e-16</v>
+        <v>2.156220662648606e-16</v>
       </c>
       <c r="Z5" t="n">
         <v>0.004341655571162808</v>
@@ -2429,25 +2429,25 @@
         <v>0.001906754858767264</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3149963511457141</v>
+        <v>0.3149963511457143</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.000357339583127474</v>
+        <v>0.0003573395831274739</v>
       </c>
       <c r="AF5" t="n">
         <v>0.0009885420389313098</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.047380247024071e-07</v>
+        <v>4.04738024702407e-07</v>
       </c>
       <c r="AH5" t="n">
         <v>0.0001080973477766001</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.003011521806965992</v>
+        <v>0.003011521806965991</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.973143537295663e-06</v>
+        <v>4.973143537295662e-06</v>
       </c>
       <c r="AK5" t="n">
         <v>0.0004999161886623939</v>
@@ -2459,7 +2459,7 @@
         <v>0.1122844533562152</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.003745497065090805</v>
+        <v>0.003745497065090808</v>
       </c>
       <c r="AO5" t="n">
         <v>0.002441121173304978</v>
@@ -2468,7 +2468,7 @@
         <v>0.003400935319957841</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.10293121390124e-14</v>
+        <v>4.102931213901238e-14</v>
       </c>
       <c r="AR5" t="n">
         <v>0.003117298856981964</v>
@@ -2492,10 +2492,10 @@
         <v>0.0003175791864021051</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0004948307446850698</v>
+        <v>0.0004948307446850697</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.002918344360815573</v>
+        <v>0.002918344360815574</v>
       </c>
       <c r="BA5" t="n">
         <v>0.0005897016143635453</v>
@@ -2504,13 +2504,13 @@
         <v>5.453632079912957e-05</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.446172703018069e-05</v>
+        <v>5.44617270301807e-05</v>
       </c>
       <c r="BD5" t="n">
         <v>9.748651414374381e-07</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.2166887086439978</v>
+        <v>0.2166887086439979</v>
       </c>
       <c r="BF5" t="n">
         <v>0.007056150216407109</v>
@@ -2519,10 +2519,10 @@
         <v>1.567630741392079e-05</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.05530733607417999</v>
+        <v>0.05530733607417998</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0004060155996983399</v>
+        <v>0.0004060155996983407</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.0003274694678268368</v>
@@ -2534,7 +2534,7 @@
         <v>0.0003326932489361758</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0001105762579146141</v>
+        <v>0.000110576257914614</v>
       </c>
       <c r="BN5" t="n">
         <v>5.797153151205086e-06</v>
@@ -2543,7 +2543,7 @@
         <v>0.001555535791495729</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0009636298647643053</v>
+        <v>0.000963629864764305</v>
       </c>
       <c r="BQ5" t="n">
         <v>0.001310539978146457</v>
@@ -2555,16 +2555,16 @@
         <v>0.01000986064651102</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.007056150216407107</v>
+        <v>0.007056150216407106</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0630285889826572</v>
+        <v>0.06302858898265724</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.1501511228111e-05</v>
+        <v>6.150151122811101e-05</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.4228954617326136</v>
+        <v>0.4228954617326141</v>
       </c>
       <c r="BX5" t="n">
         <v>4.006572702299027e-07</v>
@@ -2573,7 +2573,7 @@
         <v>0.0002220478568033525</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.03922577817246112</v>
+        <v>0.03922577817246114</v>
       </c>
       <c r="CA5" t="n">
         <v>0.0002226173504075262</v>
@@ -2591,16 +2591,16 @@
         <v>0.06798082850073409</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0006038315818877547</v>
+        <v>0.0006038315818877548</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01755184247609567</v>
+        <v>0.01755184247609569</v>
       </c>
       <c r="CH5" t="n">
         <v>0.0002355691667460505</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0004042103776876659</v>
+        <v>0.000404210377687666</v>
       </c>
       <c r="CJ5" t="n">
         <v>5.595999362299958e-05</v>
@@ -2609,16 +2609,16 @@
         <v>4.001319730385678e-05</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0004400787306061627</v>
+        <v>0.0004400787306061628</v>
       </c>
       <c r="CM5" t="n">
         <v>0.00307099318740215</v>
       </c>
       <c r="CN5" t="n">
-        <v>5.705291094758576e-05</v>
+        <v>5.705291094758575e-05</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.002045723137548829</v>
+        <v>0.002045723137548828</v>
       </c>
       <c r="CP5" t="n">
         <v>0.0002976878418848326</v>
@@ -2633,16 +2633,16 @@
         <v>0.0002459348506700313</v>
       </c>
       <c r="CT5" t="n">
-        <v>4.081369072221373e-14</v>
+        <v>4.081369072221374e-14</v>
       </c>
       <c r="CU5" t="n">
         <v>9.072878688540813e-05</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0007122774131390035</v>
+        <v>0.0007122774131390037</v>
       </c>
       <c r="CW5" t="n">
-        <v>5.461977195805135e-05</v>
+        <v>5.461977195805134e-05</v>
       </c>
       <c r="CX5" t="n">
         <v>9.79345130874569e-08</v>
@@ -2654,22 +2654,22 @@
         <v>2.220635532831832e-13</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.871062713710696e-13</v>
+        <v>1.871062713710697e-13</v>
       </c>
       <c r="DB5" t="n">
         <v>9.023615008950901e-14</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.008535975624599e-13</v>
+        <v>2.008535975624598e-13</v>
       </c>
       <c r="DD5" t="n">
         <v>2.072902565187206e-13</v>
       </c>
       <c r="DE5" t="n">
-        <v>3.258757058114758e-22</v>
+        <v>3.258757058114759e-22</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.348581049212573e-22</v>
+        <v>2.348581049212572e-22</v>
       </c>
       <c r="DG5" t="n">
         <v>1.992500678291434e-22</v>
@@ -2678,7 +2678,7 @@
         <v>1.021145470208865e-22</v>
       </c>
       <c r="DI5" t="n">
-        <v>2.135446253393462e-22</v>
+        <v>2.135446253393463e-22</v>
       </c>
       <c r="DJ5" t="n">
         <v>2.200166973018292e-22</v>
@@ -2696,7 +2696,7 @@
         <v>1.263023510401589e-13</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.422568087870603e-13</v>
+        <v>3.422568087870604e-13</v>
       </c>
       <c r="DP5" t="n">
         <v>2.856604162444378e-13</v>
@@ -2705,7 +2705,7 @@
         <v>3.204652306880447e-13</v>
       </c>
       <c r="DR5" t="n">
-        <v>2.543692161611192e-13</v>
+        <v>2.543692161611193e-13</v>
       </c>
       <c r="DS5" t="n">
         <v>2.395189815790487e-13</v>
@@ -2714,22 +2714,22 @@
         <v>2.339686876937073e-13</v>
       </c>
       <c r="DU5" t="n">
-        <v>1.365729091984679e-13</v>
+        <v>1.365729091984678e-13</v>
       </c>
       <c r="DV5" t="n">
         <v>1.115130089928615e-13</v>
       </c>
       <c r="DW5" t="n">
-        <v>2.419893436910956e-13</v>
+        <v>2.419893436910957e-13</v>
       </c>
       <c r="DX5" t="n">
-        <v>2.354925036979199e-13</v>
+        <v>2.3549250369792e-13</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.482370772208624e-13</v>
+        <v>3.482370772208626e-13</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.568843722273253e-13</v>
+        <v>2.56884372227325e-13</v>
       </c>
       <c r="EA5" t="n">
         <v>2.210295080631445e-13</v>
@@ -2744,7 +2744,7 @@
         <v>0.4277525580685092</v>
       </c>
       <c r="EE5" t="n">
-        <v>8.925190561056898</v>
+        <v>8.925190561056899</v>
       </c>
     </row>
     <row r="6">
@@ -2765,67 +2765,67 @@
         <v>10.70212849525408</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01189036978072075</v>
+        <v>0.01189036978072076</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02501669663952701</v>
+        <v>0.02501669663952702</v>
       </c>
       <c r="G6" t="n">
-        <v>3.444353810020575e-05</v>
+        <v>3.444353810020595e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008965202541531186</v>
+        <v>0.0008965202541531189</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001847573870253592</v>
+        <v>0.0001847573870253581</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008873402343727868</v>
+        <v>0.0008873402343727816</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002806509814262463</v>
+        <v>0.002806509814262458</v>
       </c>
       <c r="L6" t="n">
-        <v>2.894505097508943e-05</v>
+        <v>2.894505097508942e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>5.376168600664542e-05</v>
+        <v>5.37616860066454e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003357368920868012</v>
+        <v>0.003357368920868011</v>
       </c>
       <c r="O6" t="n">
-        <v>2.367472840552172e-05</v>
+        <v>2.367472840552033e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.652377344209496e-07</v>
+        <v>4.652377344209495e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.619345460189911e-05</v>
+        <v>5.61934546018991e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.704861621746212e-07</v>
+        <v>4.704861621746224e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.486844179037599e-06</v>
+        <v>1.486844179038531e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0004614311395605147</v>
+        <v>0.000461431139560511</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001539278865725842</v>
+        <v>0.001539278865725829</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0044866454971776</v>
+        <v>0.004486645497177603</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001722726052028818</v>
+        <v>0.0001722726052028804</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.06536288545130324</v>
+        <v>-0.06536288545130316</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.029988268689895e-16</v>
+        <v>2.029988268689896e-16</v>
       </c>
       <c r="Z6" t="n">
         <v>0.004255186042955537</v>
@@ -2840,7 +2840,7 @@
         <v>0.001868287268341994</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.3081316966891549</v>
+        <v>0.3081316966891548</v>
       </c>
       <c r="AE6" t="n">
         <v>0.0003494555130008273</v>
@@ -2849,7 +2849,7 @@
         <v>0.0009694302068937272</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.874623982824623e-07</v>
+        <v>3.874623982824622e-07</v>
       </c>
       <c r="AH6" t="n">
         <v>0.0001065971911660876</v>
@@ -2861,7 +2861,7 @@
         <v>4.87409713245572e-06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0004871613094746445</v>
+        <v>0.0004871613094746446</v>
       </c>
       <c r="AL6" t="n">
         <v>1.970647125200071e-05</v>
@@ -2870,7 +2870,7 @@
         <v>0.1122844533562152</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.002626096329272743</v>
+        <v>0.00262609632927274</v>
       </c>
       <c r="AO6" t="n">
         <v>0.002391214398531632</v>
@@ -2879,16 +2879,16 @@
         <v>0.003366145255701761</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.379134557193541e-14</v>
+        <v>3.379134557193539e-14</v>
       </c>
       <c r="AR6" t="n">
         <v>0.003047310728962225</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.056093943428338e-06</v>
+        <v>1.056093943428337e-06</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.961113015560319e-06</v>
+        <v>1.96111301556032e-06</v>
       </c>
       <c r="AU6" t="n">
         <v>2.388522775993241e-06</v>
@@ -2903,37 +2903,37 @@
         <v>0.000309703645094068</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0004771990808941917</v>
+        <v>0.0004771990808941914</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.002860073833851198</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0005750800776939879</v>
+        <v>0.0005750800776939878</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.407543708346875e-05</v>
+        <v>5.407543708346876e-05</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.304452697648916e-05</v>
+        <v>5.304452697648915e-05</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.38536975924448e-07</v>
+        <v>9.385369759244481e-07</v>
       </c>
       <c r="BE6" t="n">
         <v>0.2104268437217172</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.00701826385159968</v>
+        <v>0.007018263851599679</v>
       </c>
       <c r="BG6" t="n">
         <v>1.554024464705021e-05</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.05409533989030009</v>
+        <v>0.05409533989030006</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0003977027680355192</v>
+        <v>0.0003977027680355191</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.0003258264191339706</v>
@@ -2948,13 +2948,13 @@
         <v>0.0001075998986946025</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.684333481056811e-06</v>
+        <v>5.684333481056812e-06</v>
       </c>
       <c r="BO6" t="n">
         <v>0.001513312569936102</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.000940661205334223</v>
+        <v>0.0009406612053342231</v>
       </c>
       <c r="BQ6" t="n">
         <v>0.001295785830263042</v>
@@ -2966,31 +2966,31 @@
         <v>0.009811998819620336</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.00701826385159968</v>
+        <v>0.007018263851599678</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.06179024888818767</v>
+        <v>0.06179024888818768</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.923942172200276e-05</v>
+        <v>5.923942172200275e-05</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.4102094605841594</v>
+        <v>0.410209460584159</v>
       </c>
       <c r="BX6" t="n">
-        <v>3.927849844254926e-07</v>
+        <v>3.927849844254927e-07</v>
       </c>
       <c r="BY6" t="n">
         <v>0.0002125700820765901</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.03821414140147977</v>
+        <v>0.03821414140147975</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0002177701119423747</v>
+        <v>0.0002177701119423748</v>
       </c>
       <c r="CB6" t="n">
-        <v>9.214920070262836e-05</v>
+        <v>9.214920070262835e-05</v>
       </c>
       <c r="CC6" t="n">
         <v>0.00040663265607047</v>
@@ -2999,13 +2999,13 @@
         <v>0.0002363298431599604</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.06615840976128627</v>
+        <v>0.0661584097612863</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0005920592450422873</v>
+        <v>0.0005920592450422874</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01693314350110846</v>
+        <v>0.01693314350110845</v>
       </c>
       <c r="CH6" t="n">
         <v>0.0002309805617714514</v>
@@ -3020,7 +3020,7 @@
         <v>3.907731429189566e-05</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0004214560639714337</v>
+        <v>0.0004214560639714336</v>
       </c>
       <c r="CM6" t="n">
         <v>0.003036787473878016</v>
@@ -3035,25 +3035,25 @@
         <v>0.0002918181262821725</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0008377242831606078</v>
+        <v>0.0008377242831606079</v>
       </c>
       <c r="CR6" t="n">
         <v>1.096671158016359e-05</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0002346985522870955</v>
+        <v>0.0002346985522870956</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.358834728001808e-14</v>
+        <v>3.358834728001806e-14</v>
       </c>
       <c r="CU6" t="n">
-        <v>8.872683579214015e-05</v>
+        <v>8.872683579214016e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0006950884891075063</v>
+        <v>0.0006950884891075064</v>
       </c>
       <c r="CW6" t="n">
-        <v>5.297034240688324e-05</v>
+        <v>5.297034240688323e-05</v>
       </c>
       <c r="CX6" t="n">
         <v>9.52703777980368e-08</v>
@@ -3068,7 +3068,7 @@
         <v>1.827080277553684e-13</v>
       </c>
       <c r="DB6" t="n">
-        <v>8.779873781763904e-14</v>
+        <v>8.779873781763905e-14</v>
       </c>
       <c r="DC6" t="n">
         <v>1.957132469449924e-13</v>
@@ -3077,28 +3077,28 @@
         <v>2.016414464772749e-13</v>
       </c>
       <c r="DE6" t="n">
-        <v>3.196284890393453e-22</v>
+        <v>3.196284890393454e-22</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.28105608559677e-22</v>
+        <v>2.281056085596769e-22</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.947120580188497e-22</v>
+        <v>1.947120580188498e-22</v>
       </c>
       <c r="DH6" t="n">
-        <v>9.953768106323601e-23</v>
+        <v>9.953768106323602e-23</v>
       </c>
       <c r="DI6" t="n">
-        <v>2.08249002735666e-22</v>
+        <v>2.082490027356661e-22</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.142093681146455e-22</v>
+        <v>2.142093681146456e-22</v>
       </c>
       <c r="DK6" t="n">
         <v>1.988240523821741e-13</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.851630131625185e-13</v>
+        <v>2.851630131625186e-13</v>
       </c>
       <c r="DM6" t="n">
         <v>2.873195373249484e-13</v>
@@ -3113,7 +3113,7 @@
         <v>2.776875476806223e-13</v>
       </c>
       <c r="DQ6" t="n">
-        <v>3.176339975120627e-13</v>
+        <v>3.176339975120628e-13</v>
       </c>
       <c r="DR6" t="n">
         <v>2.470707888883947e-13</v>
@@ -3140,7 +3140,7 @@
         <v>3.415300691746408e-13</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.496702242782406e-13</v>
+        <v>2.496702242782407e-13</v>
       </c>
       <c r="EA6" t="n">
         <v>2.16040998171254e-13</v>
@@ -3152,7 +3152,7 @@
         <v>6.081593097341452e-12</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.4158808647255863</v>
+        <v>0.4158808647255862</v>
       </c>
       <c r="EE6" t="n">
         <v>8.925189746971803</v>
@@ -3173,70 +3173,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.70945930866263</v>
+        <v>10.70945930866264</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0105921303850255</v>
+        <v>0.01059213038502552</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02192663010647604</v>
+        <v>0.02192663010647613</v>
       </c>
       <c r="G7" t="n">
-        <v>3.365175639750149e-05</v>
+        <v>3.36517563975018e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008811946347664425</v>
+        <v>0.0008811946347664426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001778597138585569</v>
+        <v>0.0001778597138585571</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007550907759883166</v>
+        <v>0.0007550907759883161</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002503032023224255</v>
+        <v>0.002503032023224256</v>
       </c>
       <c r="L7" t="n">
-        <v>2.810876790959787e-05</v>
+        <v>2.810876790959785e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.821502183279261e-05</v>
+        <v>4.821502183279266e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003111359881623824</v>
+        <v>0.003111359881623829</v>
       </c>
       <c r="O7" t="n">
-        <v>1.958423547986048e-05</v>
+        <v>1.958423547986167e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.615720596321119e-07</v>
+        <v>4.615720596321115e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.537103071604749e-05</v>
+        <v>5.537103071604757e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.794018243839807e-07</v>
+        <v>3.79401824383983e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.377118890937538e-06</v>
+        <v>1.377118890937541e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004238988196865628</v>
+        <v>0.0004238988196865647</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001397575706152676</v>
+        <v>0.001397575706155396</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004454733744130519</v>
+        <v>0.004454733744130517</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001546008681306148</v>
+        <v>0.0001546008681306151</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.02630523788105665</v>
+        <v>-0.02630523788105692</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.977359672455756e-16</v>
+        <v>1.977359672455757e-16</v>
       </c>
       <c r="Z7" t="n">
         <v>0.004168118233943727</v>
@@ -3251,16 +3251,16 @@
         <v>0.001829359186765236</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3031064703763313</v>
+        <v>0.3031064703763319</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0003413997539129126</v>
+        <v>0.0003413997539129128</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0009501613024789834</v>
+        <v>0.0009501613024789836</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.739452026054256e-07</v>
+        <v>3.739452026054257e-07</v>
       </c>
       <c r="AH7" t="n">
         <v>0.0001054872287364135</v>
@@ -3275,22 +3275,22 @@
         <v>0.0004762802136847406</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.939331526094623e-05</v>
+        <v>1.939331526094624e-05</v>
       </c>
       <c r="AM7" t="n">
         <v>0.1122844533562152</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.000851723960590419</v>
+        <v>0.0008517239605904208</v>
       </c>
       <c r="AO7" t="n">
         <v>0.002340453442792825</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.003334421955887912</v>
+        <v>0.003334421955887914</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.211332965347992e-14</v>
+        <v>3.211332965347987e-14</v>
       </c>
       <c r="AR7" t="n">
         <v>0.002976686555589572</v>
@@ -3311,7 +3311,7 @@
         <v>0.001750372070328852</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0003029667037466931</v>
+        <v>0.0003029667037466932</v>
       </c>
       <c r="AY7" t="n">
         <v>0.0004633438933441996</v>
@@ -3320,22 +3320,22 @@
         <v>0.002801341684122575</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0005687764509692388</v>
+        <v>0.0005687764509692387</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.360861473091079e-05</v>
+        <v>5.36086147309108e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.184166556651388e-05</v>
+        <v>5.18416655665139e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.100193009258459e-07</v>
+        <v>9.100193009258461e-07</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.2059823651303971</v>
+        <v>0.2059823651303973</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.006998576476532007</v>
+        <v>0.006998576476532009</v>
       </c>
       <c r="BG7" t="n">
         <v>1.540014749586655e-05</v>
@@ -3344,7 +3344,7 @@
         <v>0.05390564088855432</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0003905547670997744</v>
+        <v>0.0003905547670997746</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.0003248492305326193</v>
@@ -3353,7 +3353,7 @@
         <v>0.01231001633810509</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.000316193974921504</v>
+        <v>0.0003161939749215041</v>
       </c>
       <c r="BM7" t="n">
         <v>0.0001051708576605573</v>
@@ -3362,10 +3362,10 @@
         <v>5.591139037549667e-06</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001477855144858274</v>
+        <v>0.001477855144858275</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0009176964225808077</v>
+        <v>0.0009176964225808078</v>
       </c>
       <c r="BQ7" t="n">
         <v>0.001286000520762292</v>
@@ -3374,22 +3374,22 @@
         <v>0.0007263016826635902</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.009613359136467539</v>
+        <v>0.009613359136467541</v>
       </c>
       <c r="BT7" t="n">
         <v>0.006998576476532008</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.06126384773949633</v>
+        <v>0.0612638477394963</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.746307775212311e-05</v>
+        <v>5.746307775212314e-05</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.4036087224164935</v>
+        <v>0.4036087224164939</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.862842000494973e-07</v>
+        <v>3.862842000494974e-07</v>
       </c>
       <c r="BY7" t="n">
         <v>0.0002051542620970259</v>
@@ -3401,7 +3401,7 @@
         <v>0.000213450097353366</v>
       </c>
       <c r="CB7" t="n">
-        <v>9.040788968614973e-05</v>
+        <v>9.040788968614976e-05</v>
       </c>
       <c r="CC7" t="n">
         <v>0.0003968450901429551</v>
@@ -3410,13 +3410,13 @@
         <v>0.000231496962302024</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.06511472983369435</v>
+        <v>0.0651147298336944</v>
       </c>
       <c r="CF7" t="n">
         <v>0.0005802939665626925</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01665201669039571</v>
+        <v>0.0166520166903957</v>
       </c>
       <c r="CH7" t="n">
         <v>0.0002264008983050289</v>
@@ -3425,19 +3425,19 @@
         <v>0.0003973344385938091</v>
       </c>
       <c r="CJ7" t="n">
-        <v>5.487940330011189e-05</v>
+        <v>5.487940330011187e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>3.826004313120454e-05</v>
+        <v>3.826004313120455e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0004067601692918853</v>
+        <v>0.0004067601692918854</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.003007391504082384</v>
+        <v>0.003007391504082383</v>
       </c>
       <c r="CN7" t="n">
-        <v>5.467639153526039e-05</v>
+        <v>5.46763915352604e-05</v>
       </c>
       <c r="CO7" t="n">
         <v>0.001962686707232324</v>
@@ -3452,34 +3452,34 @@
         <v>1.085199823376989e-05</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0002259197899815635</v>
+        <v>0.0002259197899815636</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.19155941946321e-14</v>
+        <v>3.191559419463214e-14</v>
       </c>
       <c r="CU7" t="n">
-        <v>8.694951042591276e-05</v>
+        <v>8.694951042591274e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0006804886940471223</v>
+        <v>0.0006804886940471225</v>
       </c>
       <c r="CW7" t="n">
         <v>5.158088105057477e-05</v>
       </c>
       <c r="CX7" t="n">
-        <v>9.310483683271985e-08</v>
+        <v>9.310483683271982e-08</v>
       </c>
       <c r="CY7" t="n">
         <v>3.024022959366497e-13</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.110214587451112e-13</v>
+        <v>2.110214587451113e-13</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.783244290493202e-13</v>
+        <v>1.783244290493203e-13</v>
       </c>
       <c r="DB7" t="n">
-        <v>8.553097911239199e-14</v>
+        <v>8.553097911239196e-14</v>
       </c>
       <c r="DC7" t="n">
         <v>1.913545573409686e-13</v>
@@ -3488,16 +3488,16 @@
         <v>1.973375226520217e-13</v>
       </c>
       <c r="DE7" t="n">
-        <v>3.153091385661083e-22</v>
+        <v>3.153091385661084e-22</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.234808163845469e-22</v>
+        <v>2.23480816384547e-22</v>
       </c>
       <c r="DG7" t="n">
         <v>1.901704775685922e-22</v>
       </c>
       <c r="DH7" t="n">
-        <v>9.711250106539523e-23</v>
+        <v>9.711250106539514e-23</v>
       </c>
       <c r="DI7" t="n">
         <v>2.037189904503623e-22</v>
@@ -3509,10 +3509,10 @@
         <v>1.93940288541467e-13</v>
       </c>
       <c r="DL7" t="n">
-        <v>2.829282460264272e-13</v>
+        <v>2.829282460264273e-13</v>
       </c>
       <c r="DM7" t="n">
-        <v>2.824745030615079e-13</v>
+        <v>2.824745030615081e-13</v>
       </c>
       <c r="DN7" t="n">
         <v>1.225692740973573e-13</v>
@@ -3533,7 +3533,7 @@
         <v>2.354693952206447e-13</v>
       </c>
       <c r="DT7" t="n">
-        <v>2.230841011237442e-13</v>
+        <v>2.230841011237443e-13</v>
       </c>
       <c r="DU7" t="n">
         <v>1.26041512359054e-13</v>
@@ -3542,28 +3542,28 @@
         <v>1.082077757197747e-13</v>
       </c>
       <c r="DW7" t="n">
-        <v>2.307942703816265e-13</v>
+        <v>2.307942703816264e-13</v>
       </c>
       <c r="DX7" t="n">
-        <v>2.247568840165986e-13</v>
+        <v>2.247568840165987e-13</v>
       </c>
       <c r="DY7" t="n">
-        <v>3.367575455381652e-13</v>
+        <v>3.367575455381653e-13</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.445911343797138e-13</v>
+        <v>2.445911343797137e-13</v>
       </c>
       <c r="EA7" t="n">
         <v>2.110487933548474e-13</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.17694020189685e-13</v>
+        <v>1.176940201896848e-13</v>
       </c>
       <c r="EC7" t="n">
         <v>6.081593097341452e-12</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.4112820540125364</v>
+        <v>0.4112820540125365</v>
       </c>
       <c r="EE7" t="n">
         <v>8.925189673409896</v>
@@ -3584,70 +3584,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.63314437056992</v>
+        <v>10.63314437056993</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0130696295744498</v>
+        <v>0.01306962957444982</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02851939885994984</v>
+        <v>0.02851939885994988</v>
       </c>
       <c r="G8" t="n">
-        <v>3.496431614450212e-05</v>
+        <v>3.4964316144502e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009136096282307255</v>
+        <v>0.0009136096282307264</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001900083916865151</v>
+        <v>0.0001900083916865155</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001025409916909158</v>
+        <v>0.001025409916909157</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003097472200252493</v>
+        <v>0.003097472200252489</v>
       </c>
       <c r="L8" t="n">
-        <v>2.955270057943437e-05</v>
+        <v>2.955270057943436e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>6.047117716638697e-05</v>
+        <v>6.047117716638711e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003483560681771163</v>
+        <v>0.003483560681771167</v>
       </c>
       <c r="O8" t="n">
         <v>2.574113704615097e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.671763139103716e-07</v>
+        <v>4.671763139103717e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.673451196834198e-05</v>
+        <v>5.673451196834197e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>5.03626604061551e-07</v>
+        <v>5.036266040615513e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.59980273436421e-06</v>
+        <v>1.599802734364209e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0005055578755445145</v>
+        <v>0.000505557875544514</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001711371843425411</v>
+        <v>0.001711371843429556</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004501520456296311</v>
+        <v>0.004501520456296312</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001878271795660551</v>
+        <v>0.0001878271795660578</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1505477145221926</v>
+        <v>-0.1505477145221927</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.074149781609144e-16</v>
+        <v>2.074149781609146e-16</v>
       </c>
       <c r="Z8" t="n">
         <v>0.004289138601667247</v>
@@ -3662,16 +3662,16 @@
         <v>0.001883461080447926</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.3112502991203168</v>
+        <v>0.311250299120317</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0003533225296023637</v>
+        <v>0.0003533225296023638</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0009769029969068359</v>
+        <v>0.0009769029969068357</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.950570512448638e-07</v>
+        <v>3.950570512448639e-07</v>
       </c>
       <c r="AH8" t="n">
         <v>0.0001072903944271731</v>
@@ -3701,7 +3701,7 @@
         <v>0.003384286382621062</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.646342569876784e-14</v>
+        <v>3.646342569876787e-14</v>
       </c>
       <c r="AR8" t="n">
         <v>0.003075321321405609</v>
@@ -3713,7 +3713,7 @@
         <v>1.97821795033613e-06</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.434873778561984e-06</v>
+        <v>2.434873778561985e-06</v>
       </c>
       <c r="AV8" t="n">
         <v>0.0001731714695003744</v>
@@ -3722,16 +3722,16 @@
         <v>0.001803329609558044</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0003129724840974101</v>
+        <v>0.0003129724840974098</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0004848945260593411</v>
+        <v>0.0004848945260593412</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002882974824866864</v>
+        <v>0.002882974824866863</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0005809750947121581</v>
+        <v>0.000580975094712158</v>
       </c>
       <c r="BB8" t="n">
         <v>5.433418831055583e-05</v>
@@ -3752,10 +3752,10 @@
         <v>1.56167185885648e-05</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0545088592638964</v>
+        <v>0.05450885926389642</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0004011931525780636</v>
+        <v>0.0004011931525780633</v>
       </c>
       <c r="BJ8" t="n">
         <v>0.0003266516393263159</v>
@@ -3776,7 +3776,7 @@
         <v>0.001531770615282525</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0009498866306972777</v>
+        <v>0.0009498866306972778</v>
       </c>
       <c r="BQ8" t="n">
         <v>0.001302167464713266</v>
@@ -3785,28 +3785,28 @@
         <v>0.0007731053492797536</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.009889478902501903</v>
+        <v>0.009889478902501905</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.007036550227844557</v>
+        <v>0.007036550227844559</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.06225687650023429</v>
+        <v>0.06225687650023425</v>
       </c>
       <c r="BV8" t="n">
         <v>6.022882214799028e-05</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.4114469075221542</v>
+        <v>0.4114469075221541</v>
       </c>
       <c r="BX8" t="n">
         <v>3.963271437975198e-07</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0002167366696234521</v>
+        <v>0.0002167366696234522</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.03860674256325698</v>
+        <v>0.03860674256325697</v>
       </c>
       <c r="CA8" t="n">
         <v>0.0002197642938303521</v>
@@ -3815,34 +3815,34 @@
         <v>9.298436114861944e-05</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0004118124033872707</v>
+        <v>0.0004118124033872708</v>
       </c>
       <c r="CD8" t="n">
         <v>0.0002386163991979561</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.06687204164521156</v>
+        <v>0.06687204164521152</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0005966446826774163</v>
+        <v>0.0005966446826774165</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0171748530297603</v>
+        <v>0.01717485302976029</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0002327677665208042</v>
+        <v>0.0002327677665208041</v>
       </c>
       <c r="CI8" t="n">
         <v>0.0004027122192429426</v>
       </c>
       <c r="CJ8" t="n">
-        <v>5.568868661769341e-05</v>
+        <v>5.568868661769343e-05</v>
       </c>
       <c r="CK8" t="n">
         <v>3.947075502569348e-05</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0004295275817894468</v>
+        <v>0.0004295275817894467</v>
       </c>
       <c r="CM8" t="n">
         <v>0.00305399918178439</v>
@@ -3854,31 +3854,31 @@
         <v>0.002020731659986994</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0002941145575208932</v>
+        <v>0.0002941145575208931</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0008467268488358466</v>
+        <v>0.0008467268488358465</v>
       </c>
       <c r="CR8" t="n">
         <v>1.103825435983998e-05</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0002396484995461169</v>
+        <v>0.000239648499546117</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.625601129783403e-14</v>
+        <v>3.625601129783401e-14</v>
       </c>
       <c r="CU8" t="n">
-        <v>8.955389059355242e-05</v>
+        <v>8.955389059355241e-05</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0007021940150020094</v>
+        <v>0.000702194015002009</v>
       </c>
       <c r="CW8" t="n">
         <v>5.371139426797967e-05</v>
       </c>
       <c r="CX8" t="n">
-        <v>9.642452698307559e-08</v>
+        <v>9.64245269830756e-08</v>
       </c>
       <c r="CY8" t="n">
         <v>3.091213212942016e-13</v>
@@ -3899,10 +3899,10 @@
         <v>2.040013582057761e-13</v>
       </c>
       <c r="DE8" t="n">
-        <v>3.222853698326029e-22</v>
+        <v>3.222853698326027e-22</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.309019542164887e-22</v>
+        <v>2.309019542164886e-22</v>
       </c>
       <c r="DG8" t="n">
         <v>1.965953433163969e-22</v>
@@ -3911,7 +3911,7 @@
         <v>1.006509626235052e-22</v>
       </c>
       <c r="DI8" t="n">
-        <v>2.104470151689477e-22</v>
+        <v>2.104470151689476e-22</v>
       </c>
       <c r="DJ8" t="n">
         <v>2.166548751550504e-22</v>
@@ -3941,7 +3941,7 @@
         <v>2.501349618431713e-13</v>
       </c>
       <c r="DS8" t="n">
-        <v>2.385359498908011e-13</v>
+        <v>2.38535949890801e-13</v>
       </c>
       <c r="DT8" t="n">
         <v>2.300461018490185e-13</v>
@@ -3953,10 +3953,10 @@
         <v>1.105190318642815e-13</v>
       </c>
       <c r="DW8" t="n">
-        <v>2.384060293751487e-13</v>
+        <v>2.384060293751486e-13</v>
       </c>
       <c r="DX8" t="n">
-        <v>2.321743741209463e-13</v>
+        <v>2.321743741209462e-13</v>
       </c>
       <c r="DY8" t="n">
         <v>3.444244077418916e-13</v>
@@ -3965,10 +3965,10 @@
         <v>2.527045411838855e-13</v>
       </c>
       <c r="EA8" t="n">
-        <v>2.181577559597014e-13</v>
+        <v>2.181577559597015e-13</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.219091948708775e-13</v>
+        <v>1.219091948708774e-13</v>
       </c>
       <c r="EC8" t="n">
         <v>6.081593097341452e-12</v>
@@ -3977,7 +3977,7 @@
         <v>0.4163165266031448</v>
       </c>
       <c r="EE8" t="n">
-        <v>8.925190186855332</v>
+        <v>8.925190186855334</v>
       </c>
     </row>
     <row r="9">
@@ -3998,70 +3998,70 @@
         <v>10.63965573583552</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01051983074420853</v>
+        <v>0.01051983074420852</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02194521471217598</v>
+        <v>0.02194521471217594</v>
       </c>
       <c r="G9" t="n">
-        <v>3.365050095597088e-05</v>
+        <v>3.365050095597067e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000881032489916614</v>
+        <v>0.000881032489916618</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001781312359758857</v>
+        <v>0.0001781312359758847</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0007563109193431276</v>
+        <v>0.0007563109193431231</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002548308545974136</v>
+        <v>0.002548308545974131</v>
       </c>
       <c r="L9" t="n">
         <v>2.82061227066911e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.792042470899467e-05</v>
+        <v>4.792042470899435e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00314072711154491</v>
+        <v>0.003140727111544897</v>
       </c>
       <c r="O9" t="n">
-        <v>2.032112541396132e-05</v>
+        <v>2.032112541396057e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.624448121493107e-07</v>
+        <v>4.624448121493108e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.554068862200804e-05</v>
+        <v>5.554068862200802e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.779091009372072e-07</v>
+        <v>3.779091009372067e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.376830646908488e-06</v>
+        <v>1.376830646908485e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0004218086588555164</v>
+        <v>0.000421808658855513</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001395187835863017</v>
+        <v>0.001395187835862959</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004462952142155598</v>
+        <v>0.0044629521421556</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0001552812779334231</v>
+        <v>0.0001552812779334222</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.01775671964052633</v>
+        <v>-0.01775671964052506</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.965784630954406e-16</v>
+        <v>1.965784630954405e-16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004178725218611677</v>
+        <v>0.004178725218611676</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01341127998494867</v>
@@ -4073,28 +4073,28 @@
         <v>0.001834721697928057</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.301553752057337</v>
+        <v>0.3015537520573369</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0003428192140235368</v>
+        <v>0.0003428192140235367</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0009523694177406793</v>
+        <v>0.0009523694177406795</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.744202081237771e-07</v>
+        <v>3.74420208123777e-07</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0001055345435578994</v>
+        <v>0.0001055345435578993</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.002898654753999865</v>
+        <v>0.002898654753999864</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.786515184000941e-06</v>
+        <v>4.786515184000939e-06</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0004767274253273436</v>
+        <v>0.0004767274253273434</v>
       </c>
       <c r="AL9" t="n">
         <v>1.940163786096887e-05</v>
@@ -4103,19 +4103,19 @@
         <v>0.1122844533562152</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.006172382952491262</v>
+        <v>-0.006172382952491273</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.002348261188933908</v>
+        <v>0.002348261188933907</v>
       </c>
       <c r="AP9" t="n">
         <v>0.003338424303266516</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.164257938069717e-14</v>
+        <v>3.164257938069713e-14</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.002988345911040505</v>
+        <v>0.002988345911040503</v>
       </c>
       <c r="AS9" t="n">
         <v>1.033050888756417e-06</v>
@@ -4124,19 +4124,19 @@
         <v>1.930596005631429e-06</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.308672568147137e-06</v>
+        <v>2.308672568147138e-06</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0001672776951592182</v>
+        <v>0.0001672776951592181</v>
       </c>
       <c r="AW9" t="n">
         <v>0.001756356950337609</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0003038524425132886</v>
+        <v>0.0003038524425132884</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0004633817957633249</v>
+        <v>0.0004633817957633248</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.002808683207993302</v>
@@ -4145,28 +4145,28 @@
         <v>0.0005655454913154385</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.368396888622898e-05</v>
+        <v>5.368396888622897e-05</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.189904569094065e-05</v>
+        <v>5.189904569094063e-05</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.103508558337658e-07</v>
+        <v>9.103508558337654e-07</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.2043722673215457</v>
+        <v>0.2043722673215455</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.006997694975182931</v>
+        <v>0.00699769497518293</v>
       </c>
       <c r="BG9" t="n">
         <v>1.542360435658668e-05</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.05386418423654354</v>
+        <v>0.05386418423654352</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0003914885415321336</v>
+        <v>0.0003914885415321335</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.0003248704996031255</v>
@@ -4175,67 +4175,67 @@
         <v>0.01231502152510149</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0003163239774251775</v>
+        <v>0.0003163239774251774</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.000105233066947353</v>
+        <v>0.0001052330669473531</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.595136203504791e-06</v>
+        <v>5.59513620350479e-06</v>
       </c>
       <c r="BO9" t="n">
         <v>0.001480040397415143</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0009214071591155739</v>
+        <v>0.0009214071591155738</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001284741707029281</v>
+        <v>0.00128474170702928</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0007279108940668279</v>
+        <v>0.0007279108940668276</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.009635671958828971</v>
+        <v>0.00963567195882897</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.006997694975182929</v>
+        <v>0.00699769497518293</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0609271836370873</v>
+        <v>0.06092718363708725</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.747941800874406e-05</v>
+        <v>5.747941800874403e-05</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.3691748969817908</v>
+        <v>0.3691748969817904</v>
       </c>
       <c r="BX9" t="n">
-        <v>3.865944490494577e-07</v>
+        <v>3.865944490494575e-07</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0002054148601898224</v>
+        <v>0.0002054148601898223</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.03760798777783939</v>
+        <v>0.03760798777783936</v>
       </c>
       <c r="CA9" t="n">
         <v>0.0002133885711273559</v>
       </c>
       <c r="CB9" t="n">
-        <v>9.035501281363078e-05</v>
+        <v>9.03550128136308e-05</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0003975572313941164</v>
+        <v>0.0003975572313941163</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0002314997224272768</v>
+        <v>0.0002314997224272767</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.06379862105503671</v>
+        <v>0.06379862105503667</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0005814459011685043</v>
+        <v>0.0005814459011685042</v>
       </c>
       <c r="CG9" t="n">
         <v>0.01649073201924521</v>
@@ -4244,22 +4244,22 @@
         <v>0.000226828971764142</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0003978929458626383</v>
+        <v>0.0003978929458626382</v>
       </c>
       <c r="CJ9" t="n">
-        <v>5.494305196220172e-05</v>
+        <v>5.494305196220173e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>3.826922190392661e-05</v>
+        <v>3.82692219039266e-05</v>
       </c>
       <c r="CL9" t="n">
         <v>0.0004071958953399582</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.003010454076548964</v>
+        <v>0.003010454076548963</v>
       </c>
       <c r="CN9" t="n">
-        <v>5.466582777695868e-05</v>
+        <v>5.466582777695867e-05</v>
       </c>
       <c r="CO9" t="n">
         <v>0.001968440049415094</v>
@@ -4268,22 +4268,22 @@
         <v>0.0002865738382000544</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0008200519082143724</v>
+        <v>0.0008200519082143723</v>
       </c>
       <c r="CR9" t="n">
         <v>1.085691873655587e-05</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0002263220877806996</v>
+        <v>0.0002263220877806995</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.144600141855095e-14</v>
+        <v>3.144600141855088e-14</v>
       </c>
       <c r="CU9" t="n">
-        <v>8.693271133608974e-05</v>
+        <v>8.69327113360897e-05</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0006823946831260229</v>
+        <v>0.0006823946831260231</v>
       </c>
       <c r="CW9" t="n">
         <v>5.172166025925958e-05</v>
@@ -4298,7 +4298,7 @@
         <v>2.114495651947206e-13</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.790328394409332e-13</v>
+        <v>1.790328394409331e-13</v>
       </c>
       <c r="DB9" t="n">
         <v>8.585887247475888e-14</v>
@@ -4307,10 +4307,10 @@
         <v>1.919345731327538e-13</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.977019270664825e-13</v>
+        <v>1.977019270664824e-13</v>
       </c>
       <c r="DE9" t="n">
-        <v>3.151428864341224e-22</v>
+        <v>3.151428864341223e-22</v>
       </c>
       <c r="DF9" t="n">
         <v>2.239242359808357e-22</v>
@@ -4319,13 +4319,13 @@
         <v>1.908926135594584e-22</v>
       </c>
       <c r="DH9" t="n">
-        <v>9.74542324874534e-23</v>
+        <v>9.745423248745341e-23</v>
       </c>
       <c r="DI9" t="n">
-        <v>2.043145734141074e-22</v>
+        <v>2.043145734141073e-22</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.101133055459047e-22</v>
+        <v>2.101133055459045e-22</v>
       </c>
       <c r="DK9" t="n">
         <v>1.941577929738904e-13</v>
@@ -4340,52 +4340,52 @@
         <v>1.227170753725771e-13</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.366031362320008e-13</v>
+        <v>3.366031362320007e-13</v>
       </c>
       <c r="DP9" t="n">
-        <v>2.71591351648719e-13</v>
+        <v>2.715913516487189e-13</v>
       </c>
       <c r="DQ9" t="n">
-        <v>3.154211734033848e-13</v>
+        <v>3.154211734033847e-13</v>
       </c>
       <c r="DR9" t="n">
-        <v>2.413342153904271e-13</v>
+        <v>2.41334215390427e-13</v>
       </c>
       <c r="DS9" t="n">
-        <v>2.357775113763809e-13</v>
+        <v>2.357775113763808e-13</v>
       </c>
       <c r="DT9" t="n">
-        <v>2.235030826610255e-13</v>
+        <v>2.235030826610254e-13</v>
       </c>
       <c r="DU9" t="n">
         <v>1.263395554775444e-13</v>
       </c>
       <c r="DV9" t="n">
-        <v>1.083738795442459e-13</v>
+        <v>1.083738795442458e-13</v>
       </c>
       <c r="DW9" t="n">
-        <v>2.312357616557136e-13</v>
+        <v>2.312357616557134e-13</v>
       </c>
       <c r="DX9" t="n">
         <v>2.254149233025322e-13</v>
       </c>
       <c r="DY9" t="n">
-        <v>3.366510630521272e-13</v>
+        <v>3.366510630521271e-13</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.450965682811796e-13</v>
+        <v>2.450965682811795e-13</v>
       </c>
       <c r="EA9" t="n">
         <v>2.118332554853552e-13</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.180971539893006e-13</v>
+        <v>1.180971539893005e-13</v>
       </c>
       <c r="EC9" t="n">
         <v>6.081593097341452e-12</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.3794328818025741</v>
+        <v>0.3794328818025739</v>
       </c>
       <c r="EE9" t="n">
         <v>8.925189744988158</v>
@@ -4409,103 +4409,103 @@
         <v>10.44316236140265</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00922886384862665</v>
+        <v>0.009228863848626662</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01915059383460893</v>
+        <v>0.01915059383460894</v>
       </c>
       <c r="G10" t="n">
-        <v>3.274896862308848e-05</v>
+        <v>3.274896862308797e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0008601806002358269</v>
+        <v>0.0008601806002358249</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001700539907640886</v>
+        <v>0.0001700539907640877</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0006328263258109277</v>
+        <v>0.0006328263258109261</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00220182944509666</v>
+        <v>0.002201829445096656</v>
       </c>
       <c r="L10" t="n">
-        <v>2.722379056363304e-05</v>
+        <v>2.722379056363303e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.329042340711879e-05</v>
+        <v>4.329042340711881e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.002859267554310283</v>
+        <v>0.002859267554310285</v>
       </c>
       <c r="O10" t="n">
-        <v>1.490704148805639e-05</v>
+        <v>1.490704148805472e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.582267167656856e-07</v>
+        <v>4.582267167656855e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.451536044885216e-05</v>
+        <v>5.451536044885213e-05</v>
       </c>
       <c r="R10" t="n">
         <v>2.250447543493167e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.277310938810218e-06</v>
+        <v>1.277310938810216e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0003903209780072621</v>
+        <v>0.0003903209780072629</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001272574603166385</v>
+        <v>0.001272574603160355</v>
       </c>
       <c r="V10" t="n">
         <v>0.00441971449285951</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0001356977020902577</v>
+        <v>0.000135697702090259</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.010517799715506</v>
+        <v>-0.01051779971550598</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.902418641443175e-16</v>
+        <v>1.902418641443176e-16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.004064904075478823</v>
+        <v>0.004064904075478824</v>
       </c>
       <c r="AA10" t="n">
         <v>0.01304587813785929</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.001544560014236826</v>
+        <v>0.001544560014236825</v>
       </c>
       <c r="AC10" t="n">
         <v>0.001784723606940508</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.2901897025078012</v>
+        <v>0.2901897025078011</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0003306520551805033</v>
+        <v>0.0003306520551805032</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0009269207113401849</v>
+        <v>0.000926920711340185</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.565122373183513e-07</v>
+        <v>3.565122373183512e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0001040689821050797</v>
+        <v>0.0001040689821050796</v>
       </c>
       <c r="AI10" t="n">
         <v>0.00281970771237831</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.656138908614556e-06</v>
+        <v>4.656138908614557e-06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.000460995122039478</v>
+        <v>0.0004609951220394781</v>
       </c>
       <c r="AL10" t="n">
         <v>1.896120112919809e-05</v>
@@ -4514,19 +4514,19 @@
         <v>0.1122844533562152</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.03012024205239534</v>
+        <v>-0.03012024205239538</v>
       </c>
       <c r="AO10" t="n">
         <v>0.002284237161557335</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.003294618952241383</v>
+        <v>0.003294618952241381</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.98993935961632e-14</v>
+        <v>2.989939359616318e-14</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.002901105079974971</v>
+        <v>0.00290110507997497</v>
       </c>
       <c r="AS10" t="n">
         <v>1.001816145358936e-06</v>
@@ -4544,28 +4544,28 @@
         <v>0.001708466026642568</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0002955101223706095</v>
+        <v>0.0002955101223706094</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0004445973684606122</v>
+        <v>0.0004445973684606123</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.002732172539979236</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0005512351057820508</v>
+        <v>0.0005512351057820507</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.302411636321642e-05</v>
+        <v>5.302411636321643e-05</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.016598377586846e-05</v>
+        <v>5.016598377586844e-05</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.719129559414416e-07</v>
+        <v>8.719129559414415e-07</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.1938899975636017</v>
+        <v>0.1938899975636018</v>
       </c>
       <c r="BF10" t="n">
         <v>0.006970402483535216</v>
@@ -4574,46 +4574,46 @@
         <v>1.522603862518e-05</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.05382887416537523</v>
+        <v>0.05382887416537525</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0003825785871683393</v>
+        <v>0.0003825785871683391</v>
       </c>
       <c r="BJ10" t="n">
         <v>0.000323652323489779</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.01213702204058918</v>
+        <v>0.01213702204058917</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0003066105979402969</v>
+        <v>0.0003066105979402967</v>
       </c>
       <c r="BM10" t="n">
         <v>0.0001020403042556515</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.465227207896944e-06</v>
+        <v>5.465227207896943e-06</v>
       </c>
       <c r="BO10" t="n">
         <v>0.00142933203069656</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0008930838385160822</v>
+        <v>0.000893083838516082</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.001284681579889073</v>
+        <v>0.001284681579889071</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0006888459417909096</v>
+        <v>0.0006888459417909094</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.009373284618338642</v>
+        <v>0.00937328461833864</v>
       </c>
       <c r="BT10" t="n">
         <v>0.006970402483535215</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0595174604476752</v>
+        <v>0.05951746044767523</v>
       </c>
       <c r="BV10" t="n">
         <v>5.508092705766765e-05</v>
@@ -4622,13 +4622,13 @@
         <v>0.2892270201575879</v>
       </c>
       <c r="BX10" t="n">
-        <v>3.775566962522777e-07</v>
+        <v>3.775566962522776e-07</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0001955901679337252</v>
+        <v>0.0001955901679337251</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.03668508290681656</v>
+        <v>0.03668508290681659</v>
       </c>
       <c r="CA10" t="n">
         <v>0.0002069594886667955</v>
@@ -4637,7 +4637,7 @@
         <v>8.778947819920397e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0003836432374310892</v>
+        <v>0.0003836432374310894</v>
       </c>
       <c r="CD10" t="n">
         <v>0.0002243621985159327</v>
@@ -4655,22 +4655,22 @@
         <v>0.000220655467137025</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0003930022742214861</v>
+        <v>0.0003930022742214862</v>
       </c>
       <c r="CJ10" t="n">
-        <v>5.423298149796294e-05</v>
+        <v>5.423298149796295e-05</v>
       </c>
       <c r="CK10" t="n">
-        <v>3.706889082037249e-05</v>
+        <v>3.706889082037248e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0003877194203359829</v>
+        <v>0.0003877194203359828</v>
       </c>
       <c r="CM10" t="n">
         <v>0.002970331999413706</v>
       </c>
       <c r="CN10" t="n">
-        <v>5.30066540771611e-05</v>
+        <v>5.300665407716111e-05</v>
       </c>
       <c r="CO10" t="n">
         <v>0.001914797993071981</v>
@@ -4679,58 +4679,58 @@
         <v>0.0002787708910438119</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0007935747320630487</v>
+        <v>0.000793574732063049</v>
       </c>
       <c r="CR10" t="n">
         <v>1.070543600870745e-05</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0002147836159418856</v>
+        <v>0.0002147836159418857</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.970915220538099e-14</v>
+        <v>2.970915220538097e-14</v>
       </c>
       <c r="CU10" t="n">
-        <v>8.429419886556739e-05</v>
+        <v>8.429419886556738e-05</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0006643318467321156</v>
+        <v>0.0006643318467321155</v>
       </c>
       <c r="CW10" t="n">
-        <v>4.975439942336368e-05</v>
+        <v>4.975439942336369e-05</v>
       </c>
       <c r="CX10" t="n">
         <v>9.025108911001868e-08</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.970465911964882e-13</v>
+        <v>2.970465911964883e-13</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.061946536053993e-13</v>
+        <v>2.061946536053994e-13</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.7353344882406e-13</v>
+        <v>1.735334488240599e-13</v>
       </c>
       <c r="DB10" t="n">
-        <v>8.293885766351878e-14</v>
+        <v>8.293885766351879e-14</v>
       </c>
       <c r="DC10" t="n">
         <v>1.865754263329476e-13</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.924587043873592e-13</v>
+        <v>1.924587043873591e-13</v>
       </c>
       <c r="DE10" t="n">
         <v>3.097158332297011e-22</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.184190006295924e-22</v>
+        <v>2.184190006295923e-22</v>
       </c>
       <c r="DG10" t="n">
         <v>1.851583020115672e-22</v>
       </c>
       <c r="DH10" t="n">
-        <v>9.43006324553032e-23</v>
+        <v>9.430063245530325e-23</v>
       </c>
       <c r="DI10" t="n">
         <v>1.987050822836853e-22</v>
@@ -4742,16 +4742,16 @@
         <v>1.890122874180156e-13</v>
       </c>
       <c r="DL10" t="n">
-        <v>2.804129752350528e-13</v>
+        <v>2.804129752350527e-13</v>
       </c>
       <c r="DM10" t="n">
-        <v>2.772522829212113e-13</v>
+        <v>2.772522829212112e-13</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.207167908924392e-13</v>
+        <v>1.207167908924391e-13</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.327912197470864e-13</v>
+        <v>3.327912197470865e-13</v>
       </c>
       <c r="DP10" t="n">
         <v>2.631346491667537e-13</v>
@@ -4760,13 +4760,13 @@
         <v>3.118146735602467e-13</v>
       </c>
       <c r="DR10" t="n">
-        <v>2.332546665880563e-13</v>
+        <v>2.332546665880564e-13</v>
       </c>
       <c r="DS10" t="n">
         <v>2.334536711565719e-13</v>
       </c>
       <c r="DT10" t="n">
-        <v>2.185709159081126e-13</v>
+        <v>2.185709159081125e-13</v>
       </c>
       <c r="DU10" t="n">
         <v>1.219524077559029e-13</v>
@@ -4775,22 +4775,22 @@
         <v>1.065148270312778e-13</v>
       </c>
       <c r="DW10" t="n">
-        <v>2.250876574335696e-13</v>
+        <v>2.250876574335695e-13</v>
       </c>
       <c r="DX10" t="n">
-        <v>2.191508153069759e-13</v>
+        <v>2.191508153069757e-13</v>
       </c>
       <c r="DY10" t="n">
         <v>3.305699464629557e-13</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.389369816980233e-13</v>
+        <v>2.389369816980232e-13</v>
       </c>
       <c r="EA10" t="n">
-        <v>2.054477551129568e-13</v>
+        <v>2.054477551129569e-13</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.14299140962257e-13</v>
+        <v>1.142991409622571e-13</v>
       </c>
       <c r="EC10" t="n">
         <v>6.081593097341452e-12</v>
@@ -4799,7 +4799,7 @@
         <v>0.3122193560559922</v>
       </c>
       <c r="EE10" t="n">
-        <v>8.925190393201378</v>
+        <v>8.925190393201385</v>
       </c>
     </row>
   </sheetData>
@@ -5516,43 +5516,43 @@
         <v>4.355772569509432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02443308738439345</v>
+        <v>0.02443308738439344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01855228952799651</v>
+        <v>0.01855228952799649</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04167523093173848</v>
+        <v>0.04167523093173846</v>
       </c>
       <c r="H2" t="n">
-        <v>3.711107245476235e-05</v>
+        <v>3.711107245476231e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001019079028989823</v>
+        <v>0.001019079028989828</v>
       </c>
       <c r="J2" t="n">
         <v>0.000207683396662165</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001588092258278459</v>
+        <v>0.001588092258278462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005588723654620951</v>
+        <v>0.0005588723654620952</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003688580575341322</v>
+        <v>0.003688580575341319</v>
       </c>
       <c r="N2" t="n">
         <v>3.152046796287712e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>9.635959780726154e-05</v>
+        <v>9.635959780726153e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003848856747473808</v>
+        <v>0.003848856747473811</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.08197596435446e-05</v>
+        <v>3.081975964354437e-05</v>
       </c>
       <c r="R2" t="n">
         <v>4.757221769782728e-07</v>
@@ -5561,40 +5561,40 @@
         <v>5.807906064559163e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.542665813998698e-07</v>
+        <v>5.542665813998705e-07</v>
       </c>
       <c r="U2" t="n">
         <v>2.194268615797422e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0006865958173996934</v>
+        <v>0.0006865958173996933</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00235663413051937</v>
+        <v>0.002356634130519373</v>
       </c>
       <c r="X2" t="n">
         <v>0.004518609097640749</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002421297367460325</v>
+        <v>0.000242129736746033</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.2288108341276214</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.609336582174571e-16</v>
+        <v>2.609336582174572e-16</v>
       </c>
       <c r="AB2" t="n">
         <v>0.00433260640399049</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.01390783511173324</v>
+        <v>0.01390783511173323</v>
       </c>
       <c r="AD2" t="n">
         <v>0.001765237714289379</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.00190290307030635</v>
+        <v>0.001902903070306349</v>
       </c>
       <c r="AF2" t="n">
         <v>0.3165948334984404</v>
@@ -5606,7 +5606,7 @@
         <v>0.0009861783438288086</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.258157553502945e-07</v>
+        <v>4.258157553502946e-07</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.0001083753711993728</v>
@@ -5615,28 +5615,28 @@
         <v>0.003005207332489796</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.962778180923354e-06</v>
+        <v>4.962778180923353e-06</v>
       </c>
       <c r="AM2" t="n">
         <v>0.0005253641280185602</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.034450695454045e-05</v>
+        <v>2.034450695454046e-05</v>
       </c>
       <c r="AO2" t="n">
         <v>0.1105267675102022</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.006425904829765032</v>
+        <v>0.006425904829765037</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.002436353729532717</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.003386299172455925</v>
+        <v>0.003386299172455926</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.573079075026743e-14</v>
+        <v>4.57307907502674e-14</v>
       </c>
       <c r="AT2" t="n">
         <v>0.003114649370157259</v>
@@ -5651,49 +5651,49 @@
         <v>2.622417715462028e-06</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0001804360585868743</v>
+        <v>0.0001804360585868742</v>
       </c>
       <c r="AY2" t="n">
         <v>0.001822371986513181</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.000320029737820652</v>
+        <v>0.0003200297378206517</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0005147443093067955</v>
+        <v>0.0005147443093067954</v>
       </c>
       <c r="BB2" t="n">
         <v>0.002912298566885623</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0005940621602104693</v>
+        <v>0.000594062160210469</v>
       </c>
       <c r="BD2" t="n">
         <v>5.411113677516979e-05</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.733340609581126e-05</v>
+        <v>5.733340609581128e-05</v>
       </c>
       <c r="BF2" t="n">
         <v>1.016783968172058e-06</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.2194109314015659</v>
+        <v>0.2194109314015661</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.006971128685576625</v>
+        <v>0.006971128685576624</v>
       </c>
       <c r="BI2" t="n">
         <v>1.556317800940356e-05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.05533900871966602</v>
+        <v>0.05533900871966597</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0004073997636041357</v>
+        <v>0.0004073997636041356</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0003236281314015077</v>
+        <v>0.0003236281314015078</v>
       </c>
       <c r="BM2" t="n">
         <v>0.01268346182786669</v>
@@ -5705,7 +5705,7 @@
         <v>0.0001133803716704812</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.878787601395595e-06</v>
+        <v>5.878787601395594e-06</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.001643823787859592</v>
@@ -5717,13 +5717,13 @@
         <v>0.001307126213413321</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0008432606072872978</v>
+        <v>0.0008432606072872979</v>
       </c>
       <c r="BU2" t="n">
         <v>0.009988625111586501</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.006971128685576624</v>
+        <v>0.006971128685576622</v>
       </c>
       <c r="BW2" t="n">
         <v>0.06304266108939789</v>
@@ -5732,7 +5732,7 @@
         <v>6.40962081214425e-05</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.435851826030366</v>
+        <v>0.4358518260303664</v>
       </c>
       <c r="BZ2" t="n">
         <v>4.064437363005253e-07</v>
@@ -5741,37 +5741,37 @@
         <v>0.0002336115464766492</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.03939774194747424</v>
+        <v>0.03939774194747426</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.0002309594676715835</v>
+        <v>0.0002309594676715836</v>
       </c>
       <c r="CD2" t="n">
-        <v>9.771592016936305e-05</v>
+        <v>9.771592016936304e-05</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0004435597976043862</v>
+        <v>0.0004435597976043861</v>
       </c>
       <c r="CF2" t="n">
         <v>0.0002516773026851111</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.06898688240593076</v>
+        <v>0.06898688240593077</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0006025035435993817</v>
+        <v>0.0006025035435993815</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.01768888102744465</v>
+        <v>0.01768888102744464</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0002350525502884576</v>
+        <v>0.0002350525502884575</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.000401059013745376</v>
+        <v>0.0004010590137453759</v>
       </c>
       <c r="CL2" t="n">
-        <v>5.570529743927592e-05</v>
+        <v>5.570529743927593e-05</v>
       </c>
       <c r="CM2" t="n">
         <v>4.17447441311793e-05</v>
@@ -5780,7 +5780,7 @@
         <v>0.0004625519986368854</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.003063044516422269</v>
+        <v>0.00306304451642227</v>
       </c>
       <c r="CP2" t="n">
         <v>5.925054573311251e-05</v>
@@ -5801,13 +5801,13 @@
         <v>0.0002599804610949213</v>
       </c>
       <c r="CV2" t="n">
-        <v>4.5469857815984e-14</v>
+        <v>4.546985781598399e-14</v>
       </c>
       <c r="CW2" t="n">
         <v>9.42235908278606e-05</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0007186731282901001</v>
+        <v>0.0007186731282901003</v>
       </c>
       <c r="CY2" t="n">
         <v>5.831293286062466e-05</v>
@@ -5825,7 +5825,7 @@
         <v>1.881805873840645e-13</v>
       </c>
       <c r="DD2" t="n">
-        <v>9.234582597599754e-14</v>
+        <v>9.234582597599751e-14</v>
       </c>
       <c r="DE2" t="n">
         <v>2.02595428807515e-13</v>
@@ -5834,10 +5834,10 @@
         <v>2.092682294466169e-13</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.260376788772748e-22</v>
+        <v>3.260376788772747e-22</v>
       </c>
       <c r="DH2" t="n">
-        <v>2.378807208279963e-22</v>
+        <v>2.378807208279965e-22</v>
       </c>
       <c r="DI2" t="n">
         <v>2.00229079094723e-22</v>
@@ -5846,13 +5846,13 @@
         <v>1.041327114748533e-22</v>
       </c>
       <c r="DK2" t="n">
-        <v>2.151924099138863e-22</v>
+        <v>2.151924099138862e-22</v>
       </c>
       <c r="DL2" t="n">
         <v>2.219017189837276e-22</v>
       </c>
       <c r="DM2" t="n">
-        <v>2.096309989775185e-13</v>
+        <v>2.096309989775184e-13</v>
       </c>
       <c r="DN2" t="n">
         <v>2.867029066339696e-13</v>
@@ -5864,55 +5864,55 @@
         <v>1.286287268719502e-13</v>
       </c>
       <c r="DQ2" t="n">
-        <v>3.398374687481556e-13</v>
+        <v>3.398374687481555e-13</v>
       </c>
       <c r="DR2" t="n">
         <v>2.863555844333919e-13</v>
       </c>
       <c r="DS2" t="n">
-        <v>3.180489050724175e-13</v>
+        <v>3.180489050724174e-13</v>
       </c>
       <c r="DT2" t="n">
         <v>2.550194037610396e-13</v>
       </c>
       <c r="DU2" t="n">
-        <v>2.378943505538931e-13</v>
+        <v>2.37894350553893e-13</v>
       </c>
       <c r="DV2" t="n">
         <v>2.353452432773793e-13</v>
       </c>
       <c r="DW2" t="n">
-        <v>1.392655055506687e-13</v>
+        <v>1.392655055506686e-13</v>
       </c>
       <c r="DX2" t="n">
         <v>1.138029419306371e-13</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.43835340782934e-13</v>
+        <v>2.438353407829341e-13</v>
       </c>
       <c r="DZ2" t="n">
         <v>2.371004049409804e-13</v>
       </c>
       <c r="EA2" t="n">
-        <v>3.483536978509382e-13</v>
+        <v>3.483536978509384e-13</v>
       </c>
       <c r="EB2" t="n">
-        <v>2.598721678717314e-13</v>
+        <v>2.598721678717313e-13</v>
       </c>
       <c r="EC2" t="n">
         <v>2.219666589482222e-13</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.255666066863826e-13</v>
+        <v>1.255666066863827e-13</v>
       </c>
       <c r="EE2" t="n">
         <v>5.986392650717769e-12</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.439059811805165</v>
+        <v>0.4390598118051651</v>
       </c>
       <c r="EG2" t="n">
-        <v>2.613105474380618</v>
+        <v>2.613105474380617</v>
       </c>
     </row>
     <row r="3">
@@ -5930,112 +5930,112 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.398443518981107</v>
+        <v>4.398443518981108</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01612914357541792</v>
+        <v>0.01612914357541803</v>
       </c>
       <c r="F3" t="n">
         <v>0.0157688216647664</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0352621525524454</v>
+        <v>0.0352621525524455</v>
       </c>
       <c r="H3" t="n">
         <v>3.618152429568153e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009794906194032099</v>
+        <v>0.0009794906194032047</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002001284746939458</v>
+        <v>0.0002001284746939455</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001332464554329938</v>
+        <v>0.00133246455432994</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005200565073010244</v>
+        <v>0.0005200565073010246</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003379392170279086</v>
+        <v>0.003379392170279085</v>
       </c>
       <c r="N3" t="n">
-        <v>3.07297472560523e-05</v>
+        <v>3.072974725605233e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>7.989072484803267e-05</v>
+        <v>7.989072484803273e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003718494301112276</v>
+        <v>0.003718494301112272</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.931204071409317e-05</v>
+        <v>2.931204071409343e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.723093556881964e-07</v>
+        <v>4.723093556881965e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.755013933489767e-05</v>
+        <v>5.755013933489771e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.400180247227017e-07</v>
+        <v>5.40018024722704e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>1.93296550611736e-06</v>
+        <v>1.932965506117361e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000598930275947854</v>
+        <v>0.000598930275947855</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002053293630764514</v>
+        <v>0.002053293630764559</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004514590744794408</v>
+        <v>0.00451459074479441</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002175691359668182</v>
+        <v>0.0002175691359668187</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.1501428016131571</v>
+        <v>-0.1501428016131569</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.418755428664302e-16</v>
+        <v>2.418755428664301e-16</v>
       </c>
       <c r="AB3" t="n">
         <v>0.004306330187853182</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01382227715887501</v>
+        <v>0.01382227715887502</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0017236468144351</v>
+        <v>0.001723646814435101</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.001891083991956053</v>
+        <v>0.001891083991956054</v>
       </c>
       <c r="AF3" t="n">
         <v>0.3126648358162972</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0003553420682435524</v>
+        <v>0.0003553420682435522</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0009804398061075549</v>
+        <v>0.0009804398061075547</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.110115706991626e-07</v>
+        <v>4.110115706991627e-07</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.0001072351686839932</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.002987067142898895</v>
+        <v>0.002987067142898896</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.932680124473235e-06</v>
+        <v>4.932680124473236e-06</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0005133161534402816</v>
+        <v>0.0005133161534402817</v>
       </c>
       <c r="AN3" t="n">
         <v>2.005483725768753e-05</v>
@@ -6044,7 +6044,7 @@
         <v>0.1105267675102022</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.006267872522606866</v>
+        <v>0.006267872522606863</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.002420848747645656</v>
@@ -6053,7 +6053,7 @@
         <v>0.003367913779135194</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.105600752928432e-14</v>
+        <v>4.105600752928438e-14</v>
       </c>
       <c r="AT3" t="n">
         <v>0.00309227207767559</v>
@@ -6065,34 +6065,34 @@
         <v>1.996529670337524e-06</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.532059510933499e-06</v>
+        <v>2.5320595109335e-06</v>
       </c>
       <c r="AX3" t="n">
         <v>0.0001764485722268811</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.001810717131793344</v>
+        <v>0.001810717131793345</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.0003161804617818887</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.000500327932501154</v>
+        <v>0.0005003279325011542</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.002894552433006144</v>
+        <v>0.002894552433006145</v>
       </c>
       <c r="BC3" t="n">
         <v>0.0005844561624127119</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.39437198668298e-05</v>
+        <v>5.394371986682982e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.598256936037734e-05</v>
+        <v>5.598256936037735e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.867199668186849e-07</v>
+        <v>9.867199668186851e-07</v>
       </c>
       <c r="BG3" t="n">
         <v>0.2157780061186911</v>
@@ -6104,13 +6104,13 @@
         <v>1.551274729517253e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.05451292932826043</v>
+        <v>0.05451292932826044</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0004033005153560175</v>
+        <v>0.0004033005153560172</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0003227447381616361</v>
+        <v>0.0003227447381616362</v>
       </c>
       <c r="BM3" t="n">
         <v>0.01253795170484614</v>
@@ -6119,88 +6119,88 @@
         <v>0.0003337854337668825</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0001109049450269848</v>
+        <v>0.0001109049450269849</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.790059858162889e-06</v>
+        <v>5.79005985816289e-06</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.001602824254617178</v>
+        <v>0.001602824254617179</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0009561765885876869</v>
+        <v>0.0009561765885876873</v>
       </c>
       <c r="BS3" t="n">
         <v>0.001297347547262148</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0008095405486594845</v>
+        <v>0.0008095405486594846</v>
       </c>
       <c r="BU3" t="n">
         <v>0.009928893452393596</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.006951636488490281</v>
+        <v>0.00695163648849028</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.06238165237896515</v>
+        <v>0.06238165237896516</v>
       </c>
       <c r="BX3" t="n">
-        <v>6.223106092684839e-05</v>
+        <v>6.223106092684837e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.4327805676591459</v>
+        <v>0.4327805676591457</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.00202381124354e-07</v>
+        <v>4.002023811243541e-07</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0002254896570744316</v>
+        <v>0.0002254896570744317</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.03883732181453653</v>
+        <v>0.03883732181453652</v>
       </c>
       <c r="CC3" t="n">
         <v>0.0002267475327625468</v>
       </c>
       <c r="CD3" t="n">
-        <v>9.589558004744281e-05</v>
+        <v>9.589558004744282e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0004319820799478286</v>
+        <v>0.0004319820799478288</v>
       </c>
       <c r="CF3" t="n">
         <v>0.0002467942437653828</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.06805830298482234</v>
+        <v>0.06805830298482232</v>
       </c>
       <c r="CH3" t="n">
         <v>0.0005989698579763599</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.01740306395135826</v>
+        <v>0.01740306395135827</v>
       </c>
       <c r="CJ3" t="n">
         <v>0.0002336853107310795</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0003998181590129736</v>
+        <v>0.0003998181590129737</v>
       </c>
       <c r="CL3" t="n">
-        <v>5.540716490555163e-05</v>
+        <v>5.540716490555164e-05</v>
       </c>
       <c r="CM3" t="n">
         <v>4.089816738134986e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0004465016951226186</v>
+        <v>0.0004465016951226188</v>
       </c>
       <c r="CO3" t="n">
         <v>0.003042527020152849</v>
       </c>
       <c r="CP3" t="n">
-        <v>5.814807854063468e-05</v>
+        <v>5.814807854063469e-05</v>
       </c>
       <c r="CQ3" t="n">
         <v>0.002028910145215948</v>
@@ -6209,25 +6209,25 @@
         <v>0.0002952845681694022</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0008801091921092052</v>
+        <v>0.0008801091921092053</v>
       </c>
       <c r="CT3" t="n">
-        <v>1.103343867026626e-05</v>
+        <v>1.103343867026625e-05</v>
       </c>
       <c r="CU3" t="n">
         <v>0.0002502023523739948</v>
       </c>
       <c r="CV3" t="n">
-        <v>4.081413263636595e-14</v>
+        <v>4.0814132636366e-14</v>
       </c>
       <c r="CW3" t="n">
-        <v>9.247038473735347e-05</v>
+        <v>9.247038473735349e-05</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0007098164823245501</v>
+        <v>0.0007098164823245499</v>
       </c>
       <c r="CY3" t="n">
-        <v>5.66640978433632e-05</v>
+        <v>5.666409784336321e-05</v>
       </c>
       <c r="CZ3" t="n">
         <v>9.824926798221387e-08</v>
@@ -6242,7 +6242,7 @@
         <v>1.863872815325048e-13</v>
       </c>
       <c r="DD3" t="n">
-        <v>9.086775567109543e-14</v>
+        <v>9.086775567109542e-14</v>
       </c>
       <c r="DE3" t="n">
         <v>2.000625900929916e-13</v>
@@ -6251,31 +6251,31 @@
         <v>2.063632836444281e-13</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.232026443270938e-22</v>
+        <v>3.232026443270936e-22</v>
       </c>
       <c r="DH3" t="n">
         <v>2.338673072041687e-22</v>
       </c>
       <c r="DI3" t="n">
-        <v>1.983846974181647e-22</v>
+        <v>1.983846974181646e-22</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.026032415846229e-22</v>
+        <v>1.026032415846228e-22</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.126041036119592e-22</v>
+        <v>2.126041036119591e-22</v>
       </c>
       <c r="DL3" t="n">
-        <v>2.189387379958441e-22</v>
+        <v>2.189387379958442e-22</v>
       </c>
       <c r="DM3" t="n">
-        <v>2.061164178096453e-13</v>
+        <v>2.061164178096454e-13</v>
       </c>
       <c r="DN3" t="n">
         <v>2.849597173589209e-13</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.915602299578958e-13</v>
+        <v>2.915602299578959e-13</v>
       </c>
       <c r="DP3" t="n">
         <v>1.267969323712251e-13</v>
@@ -6287,7 +6287,7 @@
         <v>2.833402761214667e-13</v>
       </c>
       <c r="DS3" t="n">
-        <v>3.168922800718226e-13</v>
+        <v>3.168922800718227e-13</v>
       </c>
       <c r="DT3" t="n">
         <v>2.5238066787624e-13</v>
@@ -6302,13 +6302,13 @@
         <v>1.366492224935767e-13</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.121551138632154e-13</v>
+        <v>1.121551138632155e-13</v>
       </c>
       <c r="DY3" t="n">
-        <v>2.40651405564585e-13</v>
+        <v>2.406514055645849e-13</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.342927037467436e-13</v>
+        <v>2.342927037467437e-13</v>
       </c>
       <c r="EA3" t="n">
         <v>3.452982286001505e-13</v>
@@ -6320,16 +6320,16 @@
         <v>2.199058072143445e-13</v>
       </c>
       <c r="ED3" t="n">
-        <v>1.238213755260249e-13</v>
+        <v>1.238213755260248e-13</v>
       </c>
       <c r="EE3" t="n">
         <v>5.986392650717769e-12</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.4366478079677228</v>
+        <v>0.4366478079677227</v>
       </c>
       <c r="EG3" t="n">
-        <v>2.613105542090923</v>
+        <v>2.613105542090924</v>
       </c>
     </row>
     <row r="4">
@@ -6347,79 +6347,79 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.438125122521449</v>
+        <v>4.438125122521448</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01029950137098888</v>
+        <v>0.01029950137098889</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01374219844986772</v>
+        <v>0.01374219844986771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03071928135463897</v>
+        <v>0.03071928135463893</v>
       </c>
       <c r="H4" t="n">
-        <v>3.558581075995067e-05</v>
+        <v>3.558581075995063e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000950504547549191</v>
+        <v>0.0009505045475491903</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001941168689060118</v>
+        <v>0.0001941168689060122</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001157182598009482</v>
+        <v>0.001157182598009476</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004913772628700002</v>
+        <v>0.0004913772628700004</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003209715869429784</v>
+        <v>0.00320971586942978</v>
       </c>
       <c r="N4" t="n">
-        <v>3.014914733453491e-05</v>
+        <v>3.014914733453487e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>6.857146497052925e-05</v>
+        <v>6.85714649705293e-05</v>
       </c>
       <c r="P4" t="n">
         <v>0.003646501527607014</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.814252474244337e-05</v>
+        <v>2.814252474244216e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.694387028624423e-07</v>
+        <v>4.694387028624427e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.709313004322674e-05</v>
+        <v>5.709313004322671e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>5.23403793731917e-07</v>
+        <v>5.234037937319164e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.731769595379539e-06</v>
+        <v>1.731769595379541e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0005339368057573625</v>
+        <v>0.0005339368057573644</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001829534209154274</v>
+        <v>0.001829534209154421</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004505771588607392</v>
+        <v>0.004505771588607391</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000198256347159472</v>
+        <v>0.0001982563471594726</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.09480809726423262</v>
+        <v>-0.0948080972642326</v>
       </c>
       <c r="AA4" t="n">
         <v>2.265061657025066e-16</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004290903658054404</v>
+        <v>0.004290903658054405</v>
       </c>
       <c r="AC4" t="n">
         <v>0.01377077815390507</v>
@@ -6431,7 +6431,7 @@
         <v>0.001883853247940751</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3104197284992664</v>
+        <v>0.3104197284992666</v>
       </c>
       <c r="AG4" t="n">
         <v>0.0003552108219186696</v>
@@ -6440,13 +6440,13 @@
         <v>0.0009770974300001829</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.017425560273491e-07</v>
+        <v>4.017425560273488e-07</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.0001064902573982235</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.002976507006962915</v>
+        <v>0.002976507006962914</v>
       </c>
       <c r="AL4" t="n">
         <v>4.915009826653834e-06</v>
@@ -6461,10 +6461,10 @@
         <v>0.1105267675102022</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.006199124564517223</v>
+        <v>0.006199124564517221</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00241098163453051</v>
+        <v>0.002410981634530509</v>
       </c>
       <c r="AR4" t="n">
         <v>0.003357838765021045</v>
@@ -6500,7 +6500,7 @@
         <v>0.002884046051765357</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0005792241211766238</v>
+        <v>0.0005792241211766234</v>
       </c>
       <c r="BD4" t="n">
         <v>5.387688643478287e-05</v>
@@ -6512,19 +6512,19 @@
         <v>9.688023088413628e-07</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.2137508042267042</v>
+        <v>0.2137508042267043</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.006939845442904994</v>
+        <v>0.006939845442904995</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.549254950097691e-05</v>
+        <v>1.54925495009769e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0539318698390781</v>
+        <v>0.05393186983907811</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0004006008617437748</v>
+        <v>0.0004006008617437751</v>
       </c>
       <c r="BL4" t="n">
         <v>0.0003222357532185715</v>
@@ -6542,13 +6542,13 @@
         <v>5.736030164936351e-06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001574372901288316</v>
+        <v>0.001574372901288317</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0009516380686699276</v>
+        <v>0.0009516380686699277</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001293272719610954</v>
+        <v>0.001293272719610953</v>
       </c>
       <c r="BT4" t="n">
         <v>0.0007876738682198497</v>
@@ -6557,13 +6557,13 @@
         <v>0.009894713369427013</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.006939845442904993</v>
+        <v>0.006939845442904994</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0620010200100096</v>
+        <v>0.06200102001000959</v>
       </c>
       <c r="BX4" t="n">
-        <v>6.112551341357195e-05</v>
+        <v>6.112551341357193e-05</v>
       </c>
       <c r="BY4" t="n">
         <v>0.4344675706989444</v>
@@ -6575,7 +6575,7 @@
         <v>0.0002204044792138428</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.03849824477645416</v>
+        <v>0.03849824477645414</v>
       </c>
       <c r="CC4" t="n">
         <v>0.0002239540200939979</v>
@@ -6590,10 +6590,10 @@
         <v>0.0002435221148749532</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.06781749696828059</v>
+        <v>0.06781749696828054</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.000597014436642686</v>
+        <v>0.0005970144366426858</v>
       </c>
       <c r="CI4" t="n">
         <v>0.01721889541517516</v>
@@ -6602,7 +6602,7 @@
         <v>0.0002329437286012741</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0003993228053401551</v>
+        <v>0.000399322805340155</v>
       </c>
       <c r="CL4" t="n">
         <v>5.524370331901936e-05</v>
@@ -6623,10 +6623,10 @@
         <v>0.002021152409466233</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0002942815801304806</v>
+        <v>0.0002942815801304805</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0008667472039847535</v>
+        <v>0.0008667472039847534</v>
       </c>
       <c r="CT4" t="n">
         <v>1.095643392753851e-05</v>
@@ -6635,16 +6635,16 @@
         <v>0.0002439535155157921</v>
       </c>
       <c r="CV4" t="n">
-        <v>3.762494964422566e-14</v>
+        <v>3.762494964422564e-14</v>
       </c>
       <c r="CW4" t="n">
-        <v>9.130360878513991e-05</v>
+        <v>9.130360878513987e-05</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0007039211262852993</v>
+        <v>0.0007039211262852991</v>
       </c>
       <c r="CY4" t="n">
-        <v>5.550995331742899e-05</v>
+        <v>5.550995331742897e-05</v>
       </c>
       <c r="CZ4" t="n">
         <v>9.685098368170988e-08</v>
@@ -6653,37 +6653,37 @@
         <v>3.090323873816226e-13</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.18537643803796e-13</v>
+        <v>2.185376438037959e-13</v>
       </c>
       <c r="DC4" t="n">
         <v>1.852111644754261e-13</v>
       </c>
       <c r="DD4" t="n">
-        <v>8.98709437366964e-14</v>
+        <v>8.987094373669637e-14</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.983930391517305e-13</v>
+        <v>1.983930391517304e-13</v>
       </c>
       <c r="DF4" t="n">
         <v>2.046171763344482e-13</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.220906412277774e-22</v>
+        <v>3.220906412277776e-22</v>
       </c>
       <c r="DH4" t="n">
         <v>2.31152751792771e-22</v>
       </c>
       <c r="DI4" t="n">
-        <v>1.971877887108585e-22</v>
+        <v>1.971877887108584e-22</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.015852485933675e-22</v>
+        <v>1.015852485933674e-22</v>
       </c>
       <c r="DK4" t="n">
         <v>2.10910861688344e-22</v>
       </c>
       <c r="DL4" t="n">
-        <v>2.171678398627281e-22</v>
+        <v>2.171678398627282e-22</v>
       </c>
       <c r="DM4" t="n">
         <v>2.040035350522165e-13</v>
@@ -6698,16 +6698,16 @@
         <v>1.255458164610077e-13</v>
       </c>
       <c r="DQ4" t="n">
-        <v>3.377630717034163e-13</v>
+        <v>3.377630717034162e-13</v>
       </c>
       <c r="DR4" t="n">
-        <v>2.817528948816859e-13</v>
+        <v>2.817528948816858e-13</v>
       </c>
       <c r="DS4" t="n">
         <v>3.16352163116476e-13</v>
       </c>
       <c r="DT4" t="n">
-        <v>2.51014697532064e-13</v>
+        <v>2.510146975320639e-13</v>
       </c>
       <c r="DU4" t="n">
         <v>2.36102084569981e-13</v>
@@ -6722,16 +6722,16 @@
         <v>1.110150957976899e-13</v>
       </c>
       <c r="DY4" t="n">
-        <v>2.387144383652038e-13</v>
+        <v>2.387144383652036e-13</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.324338536078294e-13</v>
+        <v>2.324338536078295e-13</v>
       </c>
       <c r="EA4" t="n">
-        <v>3.440226409018042e-13</v>
+        <v>3.440226409018043e-13</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.527499408411744e-13</v>
+        <v>2.527499408411743e-13</v>
       </c>
       <c r="EC4" t="n">
         <v>2.185452342270122e-13</v>
@@ -6743,10 +6743,10 @@
         <v>5.986392650717769e-12</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.4390912615973645</v>
+        <v>0.4390912615973643</v>
       </c>
       <c r="EG4" t="n">
-        <v>2.613105373883237</v>
+        <v>2.613105373883235</v>
       </c>
     </row>
     <row r="5">
@@ -6767,91 +6767,91 @@
         <v>4.359807183591137</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01540019570577539</v>
+        <v>0.01540019570577542</v>
       </c>
       <c r="F5" t="n">
-        <v>0.015009884513541</v>
+        <v>0.01500988451354102</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03413843584946699</v>
+        <v>0.03413843584946703</v>
       </c>
       <c r="H5" t="n">
-        <v>3.581479037255498e-05</v>
+        <v>3.581479037255482e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009626207539243134</v>
+        <v>0.0009626207539243145</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001974297456720539</v>
+        <v>0.000197429745672054</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001281528264248147</v>
+        <v>0.001281528264248156</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005117952615024155</v>
+        <v>0.0005117952615024154</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003334666052550513</v>
+        <v>0.003334666052550517</v>
       </c>
       <c r="N5" t="n">
         <v>3.036914275775102e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>7.726431197609175e-05</v>
+        <v>7.726431197609167e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003672515688834676</v>
+        <v>0.00367251568883468</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.761899199809431e-05</v>
+        <v>2.761899199809543e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.684579518107721e-07</v>
+        <v>4.684579518107722e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>5.729359103275018e-05</v>
+        <v>5.729359103275021e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>5.24526386117127e-07</v>
+        <v>5.24526386117135e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.785032402260067e-06</v>
+        <v>1.785032402260068e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.000580858321379642</v>
+        <v>0.0005808583213796425</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001996533454973917</v>
+        <v>0.001996533454973911</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004506676414325724</v>
+        <v>0.004506676414325722</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000209941761130004</v>
+        <v>0.0002099417611300026</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1433485761145092</v>
+        <v>-0.1433485761145093</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.122467472190483e-16</v>
+        <v>2.122467472190482e-16</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004273691874341065</v>
+        <v>0.004273691874341066</v>
       </c>
       <c r="AC5" t="n">
         <v>0.01371819237864526</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.001650572872148281</v>
+        <v>0.00165057287214828</v>
       </c>
       <c r="AE5" t="n">
         <v>0.001876906772706413</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3100654403080567</v>
+        <v>0.3100654403080569</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0003517458369880076</v>
+        <v>0.0003517458369880075</v>
       </c>
       <c r="AH5" t="n">
         <v>0.0009730675337965137</v>
@@ -6878,7 +6878,7 @@
         <v>0.1105267675102022</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.003686865553952677</v>
+        <v>0.00368686555395268</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.00240290818827927</v>
@@ -6887,13 +6887,13 @@
         <v>0.003347697532388696</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.038704476305061e-14</v>
+        <v>4.038704476305058e-14</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.00306850107674673</v>
+        <v>0.003068501076746732</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.067103392254015e-06</v>
+        <v>1.067103392254016e-06</v>
       </c>
       <c r="AV5" t="n">
         <v>1.968014107695797e-06</v>
@@ -6908,31 +6908,31 @@
         <v>0.001797330175642185</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0003126078442060803</v>
+        <v>0.0003126078442060804</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0004870847302537952</v>
+        <v>0.0004870847302537951</v>
       </c>
       <c r="BB5" t="n">
         <v>0.002872660987708483</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0005804705040009238</v>
+        <v>0.000580470504000924</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.368261651240917e-05</v>
+        <v>5.368261651240918e-05</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.360919042436323e-05</v>
+        <v>5.360919042436324e-05</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.596047326305278e-07</v>
+        <v>9.59604732630528e-07</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.2132966925207494</v>
+        <v>0.2132966925207495</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00694569418271762</v>
+        <v>0.006945694182717621</v>
       </c>
       <c r="BI5" t="n">
         <v>1.543091259001062e-05</v>
@@ -6941,16 +6941,16 @@
         <v>0.05444156241725281</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0003996598856923569</v>
+        <v>0.0003996598856923575</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0003223433044854633</v>
+        <v>0.0003223433044854632</v>
       </c>
       <c r="BM5" t="n">
         <v>0.01243347290312942</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.000327485313222546</v>
+        <v>0.0003274853132225461</v>
       </c>
       <c r="BO5" t="n">
         <v>0.0001088453119320476</v>
@@ -6962,28 +6962,28 @@
         <v>0.001531185641836052</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0009485453314788426</v>
+        <v>0.0009485453314788428</v>
       </c>
       <c r="BS5" t="n">
         <v>0.00129002496024888</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.000782076456005723</v>
+        <v>0.0007820764560057229</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.009853167623986176</v>
+        <v>0.009853167623986175</v>
       </c>
       <c r="BV5" t="n">
         <v>0.00694569418271762</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.06204194786327143</v>
+        <v>0.06204194786327148</v>
       </c>
       <c r="BX5" t="n">
         <v>6.053877478007293e-05</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.4162755126193337</v>
+        <v>0.4162755126193338</v>
       </c>
       <c r="BZ5" t="n">
         <v>3.943854347982314e-07</v>
@@ -6992,40 +6992,40 @@
         <v>0.0002185719492901136</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.03861174307649064</v>
+        <v>0.03861174307649065</v>
       </c>
       <c r="CC5" t="n">
         <v>0.000219132528117419</v>
       </c>
       <c r="CD5" t="n">
-        <v>9.271983122951861e-05</v>
+        <v>9.271983122951862e-05</v>
       </c>
       <c r="CE5" t="n">
         <v>0.0004118372025060339</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0002380320528058578</v>
+        <v>0.0002380320528058579</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.06691666568491746</v>
+        <v>0.06691666568491747</v>
       </c>
       <c r="CH5" t="n">
         <v>0.0005943792828994635</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01727708827665354</v>
+        <v>0.01727708827665355</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0002318815984516843</v>
+        <v>0.0002318815984516842</v>
       </c>
       <c r="CK5" t="n">
         <v>0.0003978829223860914</v>
       </c>
       <c r="CL5" t="n">
-        <v>5.508400335191468e-05</v>
+        <v>5.508400335191469e-05</v>
       </c>
       <c r="CM5" t="n">
-        <v>3.938683605390175e-05</v>
+        <v>3.938683605390177e-05</v>
       </c>
       <c r="CN5" t="n">
         <v>0.0004331897968954209</v>
@@ -7034,7 +7034,7 @@
         <v>0.00302292026993801</v>
       </c>
       <c r="CP5" t="n">
-        <v>5.615981229457559e-05</v>
+        <v>5.615981229457557e-05</v>
       </c>
       <c r="CQ5" t="n">
         <v>0.002013699660600299</v>
@@ -7052,13 +7052,13 @@
         <v>0.0002420850193430474</v>
       </c>
       <c r="CV5" t="n">
-        <v>4.017479865513114e-14</v>
+        <v>4.017479865513112e-14</v>
       </c>
       <c r="CW5" t="n">
-        <v>8.930853056525217e-05</v>
+        <v>8.930853056525218e-05</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0007011275175827826</v>
+        <v>0.0007011275175827827</v>
       </c>
       <c r="CY5" t="n">
         <v>5.376476133802758e-05</v>
@@ -7070,22 +7070,22 @@
         <v>3.077436323042524e-13</v>
       </c>
       <c r="DB5" t="n">
-        <v>2.185874000593442e-13</v>
+        <v>2.185874000593443e-13</v>
       </c>
       <c r="DC5" t="n">
         <v>1.841773347724661e-13</v>
       </c>
       <c r="DD5" t="n">
-        <v>8.882360544000297e-14</v>
+        <v>8.882360544000298e-14</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.977094621545388e-13</v>
+        <v>1.977094621545387e-13</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.040453625106117e-13</v>
+        <v>2.040453625106118e-13</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.207744910079697e-22</v>
+        <v>3.207744910079699e-22</v>
       </c>
       <c r="DH5" t="n">
         <v>2.311816674937895e-22</v>
@@ -7097,16 +7097,16 @@
         <v>1.005160595312495e-22</v>
       </c>
       <c r="DK5" t="n">
-        <v>2.102018262765019e-22</v>
+        <v>2.102018262765021e-22</v>
       </c>
       <c r="DL5" t="n">
-        <v>2.165725852883244e-22</v>
+        <v>2.165725852883243e-22</v>
       </c>
       <c r="DM5" t="n">
         <v>2.035158740333843e-13</v>
       </c>
       <c r="DN5" t="n">
-        <v>2.838012698704095e-13</v>
+        <v>2.838012698704096e-13</v>
       </c>
       <c r="DO5" t="n">
         <v>2.906392009646428e-13</v>
@@ -7118,10 +7118,10 @@
         <v>3.368991663839921e-13</v>
       </c>
       <c r="DR5" t="n">
-        <v>2.811887262162009e-13</v>
+        <v>2.811887262162008e-13</v>
       </c>
       <c r="DS5" t="n">
-        <v>3.154487107399741e-13</v>
+        <v>3.15448710739974e-13</v>
       </c>
       <c r="DT5" t="n">
         <v>2.503873544024887e-13</v>
@@ -7142,25 +7142,25 @@
         <v>2.382012748037453e-13</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.318061354766769e-13</v>
+        <v>2.31806135476677e-13</v>
       </c>
       <c r="EA5" t="n">
-        <v>3.427858204939293e-13</v>
+        <v>3.427858204939296e-13</v>
       </c>
       <c r="EB5" t="n">
         <v>2.528631385513372e-13</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.175695416451638e-13</v>
+        <v>2.17569541645164e-13</v>
       </c>
       <c r="ED5" t="n">
-        <v>1.216521737761657e-13</v>
+        <v>1.216521737761658e-13</v>
       </c>
       <c r="EE5" t="n">
         <v>5.986392650717769e-12</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.4210565766174737</v>
+        <v>0.4210565766174739</v>
       </c>
       <c r="EG5" t="n">
         <v>2.613105527910498</v>
@@ -7181,73 +7181,73 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.401487868320756</v>
+        <v>4.401487868320755</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003389924777632243</v>
+        <v>0.003389924777632223</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01188900747084984</v>
+        <v>0.01188900747084983</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02501383041304306</v>
+        <v>0.02501383041304302</v>
       </c>
       <c r="H6" t="n">
-        <v>3.444353810020575e-05</v>
+        <v>3.444353810020595e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008965202541531186</v>
+        <v>0.0008965202541531189</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001847573870253592</v>
+        <v>0.0001847573870253581</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008873402343727868</v>
+        <v>0.0008873402343727816</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004624880381826194</v>
+        <v>0.0004624880381826197</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002806509814262463</v>
+        <v>0.002806509814262458</v>
       </c>
       <c r="N6" t="n">
-        <v>2.894505097508943e-05</v>
+        <v>2.894505097508942e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>5.376168600664542e-05</v>
+        <v>5.37616860066454e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003357368920868012</v>
+        <v>0.003357368920868011</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.367472840552172e-05</v>
+        <v>2.367472840552033e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.652377344209496e-07</v>
+        <v>4.652377344209495e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.619345460189911e-05</v>
+        <v>5.61934546018991e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.704861621746212e-07</v>
+        <v>4.704861621746224e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.486673827522977e-06</v>
+        <v>1.486673827523731e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0004613782722226825</v>
+        <v>0.000461378272222679</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001539102506635962</v>
+        <v>0.001539102506635956</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0044866454971776</v>
+        <v>0.004486645497177603</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001722726052028818</v>
+        <v>0.0001722726052028804</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.02974032261364094</v>
+        <v>-0.02974032261364095</v>
       </c>
       <c r="AA6" t="n">
         <v>1.998211103278317e-16</v>
@@ -7262,7 +7262,7 @@
         <v>0.001607621756005123</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.001839041348807317</v>
+        <v>0.001839041348807316</v>
       </c>
       <c r="AF6" t="n">
         <v>0.3033082442361218</v>
@@ -7271,10 +7271,10 @@
         <v>0.0003439851830428215</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0009542548758267546</v>
+        <v>0.0009542548758267548</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.813971136151108e-07</v>
+        <v>3.813971136151109e-07</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.0001049285329633089</v>
@@ -7301,13 +7301,13 @@
         <v>0.00235378264749707</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.003313452067154981</v>
+        <v>0.00331345206715498</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.326238035854917e-14</v>
+        <v>3.326238035854915e-14</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.002999608533541561</v>
+        <v>0.002999608533541562</v>
       </c>
       <c r="AU6" t="n">
         <v>1.03956198979683e-06</v>
@@ -7319,34 +7319,34 @@
         <v>2.35113315925864e-06</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0001684203448918649</v>
+        <v>0.000168420344891865</v>
       </c>
       <c r="AY6" t="n">
         <v>0.001760485549692521</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0003048555855705152</v>
+        <v>0.0003048555855705153</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0004697290701745666</v>
+        <v>0.0004697290701745665</v>
       </c>
       <c r="BB6" t="n">
         <v>0.002815302619795727</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.000566077850914827</v>
+        <v>0.0005660778509148267</v>
       </c>
       <c r="BD6" t="n">
         <v>5.322894740891828e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.221417503115572e-05</v>
+        <v>5.221417503115571e-05</v>
       </c>
       <c r="BF6" t="n">
         <v>9.238452433716896e-07</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.2071328499961791</v>
+        <v>0.207132849996179</v>
       </c>
       <c r="BH6" t="n">
         <v>0.006908400886008116</v>
@@ -7355,13 +7355,13 @@
         <v>1.529697973153206e-05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.05324853865986786</v>
+        <v>0.05324853865986782</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.000391477181986856</v>
+        <v>0.0003914771819868559</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0003207259758575361</v>
+        <v>0.000320725975857536</v>
       </c>
       <c r="BM6" t="n">
         <v>0.01225075570816156</v>
@@ -7373,64 +7373,64 @@
         <v>0.0001059155442420057</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.595351683443431e-06</v>
+        <v>5.595351683443432e-06</v>
       </c>
       <c r="BQ6" t="n">
         <v>0.001489623376951106</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0009259362203778088</v>
+        <v>0.0009259362203778087</v>
       </c>
       <c r="BS6" t="n">
         <v>0.001275501771827168</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0007443639449500333</v>
+        <v>0.0007443639449500329</v>
       </c>
       <c r="BU6" t="n">
         <v>0.00965840309972465</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.006908400886008116</v>
+        <v>0.006908400886008115</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.06082299257935717</v>
+        <v>0.06082299257935713</v>
       </c>
       <c r="BX6" t="n">
         <v>5.831209572116773e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.4037880964396325</v>
+        <v>0.4037880964396321</v>
       </c>
       <c r="BZ6" t="n">
         <v>3.866363807050741e-07</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0002092425383839069</v>
+        <v>0.0002092425383839068</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.03761594233249703</v>
+        <v>0.03761594233249702</v>
       </c>
       <c r="CC6" t="n">
         <v>0.0002143611676762306</v>
       </c>
       <c r="CD6" t="n">
-        <v>9.070670941416314e-05</v>
+        <v>9.07067094141631e-05</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0004002672827463974</v>
+        <v>0.0004002672827463973</v>
       </c>
       <c r="CF6" t="n">
         <v>0.0002326303673385398</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.06512277484517522</v>
+        <v>0.06512277484517523</v>
       </c>
       <c r="CH6" t="n">
         <v>0.0005827912286436984</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01666807433284182</v>
+        <v>0.01666807433284181</v>
       </c>
       <c r="CJ6" t="n">
         <v>0.0002273648228869072</v>
@@ -7439,7 +7439,7 @@
         <v>0.0003945204337366882</v>
       </c>
       <c r="CL6" t="n">
-        <v>5.452613980975442e-05</v>
+        <v>5.452613980975444e-05</v>
       </c>
       <c r="CM6" t="n">
         <v>3.846560322969577e-05</v>
@@ -7460,7 +7460,7 @@
         <v>0.0002872500442828861</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0008246106590447063</v>
+        <v>0.0008246106590447064</v>
       </c>
       <c r="CT6" t="n">
         <v>1.079504014083611e-05</v>
@@ -7469,22 +7469,22 @@
         <v>0.000231024612475267</v>
       </c>
       <c r="CV6" t="n">
-        <v>3.306255977479894e-14</v>
+        <v>3.306255977479893e-14</v>
       </c>
       <c r="CW6" t="n">
-        <v>8.733791774719396e-05</v>
+        <v>8.733791774719395e-05</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0006842076666738351</v>
+        <v>0.0006842076666738353</v>
       </c>
       <c r="CY6" t="n">
-        <v>5.214115173690088e-05</v>
+        <v>5.214115173690086e-05</v>
       </c>
       <c r="CZ6" t="n">
         <v>9.377902801990963e-08</v>
       </c>
       <c r="DA6" t="n">
-        <v>3.017521565297121e-13</v>
+        <v>3.017521565297122e-13</v>
       </c>
       <c r="DB6" t="n">
         <v>2.121009779888683e-13</v>
@@ -7496,7 +7496,7 @@
         <v>8.642434809451055e-14</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.926495778995444e-13</v>
+        <v>1.926495778995445e-13</v>
       </c>
       <c r="DF6" t="n">
         <v>1.984849781875971e-13</v>
@@ -7511,13 +7511,13 @@
         <v>1.916640614512211e-22</v>
       </c>
       <c r="DJ6" t="n">
-        <v>9.797953148936065e-23</v>
+        <v>9.797953148936061e-23</v>
       </c>
       <c r="DK6" t="n">
         <v>2.049891006422429e-22</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.108561632571214e-22</v>
+        <v>2.108561632571213e-22</v>
       </c>
       <c r="DM6" t="n">
         <v>1.957116872036178e-13</v>
@@ -7529,7 +7529,7 @@
         <v>2.82821875636763e-13</v>
       </c>
       <c r="DP6" t="n">
-        <v>1.221486156383905e-13</v>
+        <v>1.221486156383904e-13</v>
       </c>
       <c r="DQ6" t="n">
         <v>3.337129093051095e-13</v>
@@ -7541,7 +7541,7 @@
         <v>3.126617973102384e-13</v>
       </c>
       <c r="DT6" t="n">
-        <v>2.432031757361563e-13</v>
+        <v>2.432031757361562e-13</v>
       </c>
       <c r="DU6" t="n">
         <v>2.335839851997698e-13</v>
@@ -7562,13 +7562,13 @@
         <v>2.26144396184529e-13</v>
       </c>
       <c r="EA6" t="n">
-        <v>3.361838030564656e-13</v>
+        <v>3.361838030564658e-13</v>
       </c>
       <c r="EB6" t="n">
-        <v>2.457619199113615e-13</v>
+        <v>2.457619199113614e-13</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.126591212212947e-13</v>
+        <v>2.126591212212948e-13</v>
       </c>
       <c r="ED6" t="n">
         <v>1.186770985377866e-13</v>
@@ -7577,7 +7577,7 @@
         <v>5.986392650717769e-12</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.4093707211776031</v>
+        <v>0.4093707211776029</v>
       </c>
       <c r="EG6" t="n">
         <v>2.613105331936109</v>
@@ -7598,79 +7598,79 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.386002437418029</v>
+        <v>4.386002437418036</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00145908725319681</v>
+        <v>0.001459087253196636</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01059091681774009</v>
+        <v>0.01059091681774011</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02192411791676464</v>
+        <v>0.02192411791676461</v>
       </c>
       <c r="H7" t="n">
-        <v>3.365175639750149e-05</v>
+        <v>3.36517563975018e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008811946347664425</v>
+        <v>0.0008811946347664426</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001778597138585569</v>
+        <v>0.0001778597138585571</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007550907759883166</v>
+        <v>0.0007550907759883161</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004494440609618415</v>
+        <v>0.0004494440609618411</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002503032023224255</v>
+        <v>0.002503032023224256</v>
       </c>
       <c r="N7" t="n">
-        <v>2.810876790959787e-05</v>
+        <v>2.810876790959785e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.821502183279261e-05</v>
+        <v>4.821502183279266e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003111359881623824</v>
+        <v>0.003111359881623829</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.958423547986048e-05</v>
+        <v>1.958423547986167e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.615720596321119e-07</v>
+        <v>4.615720596321115e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>5.537103071604749e-05</v>
+        <v>5.537103071604757e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.794018243839807e-07</v>
+        <v>3.79401824383983e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.376961110927906e-06</v>
+        <v>1.376961110927912e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0004238502525219638</v>
+        <v>0.0004238502525219627</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001397415582353745</v>
+        <v>0.001397415582353333</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004454733744130519</v>
+        <v>0.004454733744130517</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001546008681306148</v>
+        <v>0.0001546008681306151</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.01196896764286882</v>
+        <v>-0.01196896764286903</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.946406348065186e-16</v>
+        <v>1.946406348065187e-16</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.004102871067436452</v>
+        <v>0.004102871067436453</v>
       </c>
       <c r="AC7" t="n">
         <v>0.01316481407104577</v>
@@ -7682,16 +7682,16 @@
         <v>0.001800722642223752</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2983616821452723</v>
+        <v>0.2983616821452727</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0003360555277324509</v>
+        <v>0.0003360555277324511</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.000935287604269861</v>
+        <v>0.0009352876042698609</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.680915143150361e-07</v>
+        <v>3.680915143150364e-07</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.00010383594573736</v>
@@ -7700,19 +7700,19 @@
         <v>0.00284625067624195</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.699628148511603e-06</v>
+        <v>4.699628148511602e-06</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.000468824586789769</v>
+        <v>0.0004688245867897691</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.908973489231501e-05</v>
+        <v>1.908973489231502e-05</v>
       </c>
       <c r="AO7" t="n">
         <v>0.1105267675102022</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0008383911873926001</v>
+        <v>0.0008383911873926002</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.002303816296984236</v>
@@ -7721,10 +7721,10 @@
         <v>0.003282225359642249</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.161063187731314e-14</v>
+        <v>3.161063187731309e-14</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.00293008990155254</v>
+        <v>0.002930089901552541</v>
       </c>
       <c r="AU7" t="n">
         <v>1.016842723369574e-06</v>
@@ -7742,10 +7742,10 @@
         <v>0.001722971979565499</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0002982241034037996</v>
+        <v>0.0002982241034037995</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0004560907698812029</v>
+        <v>0.000456090769881203</v>
       </c>
       <c r="BB7" t="n">
         <v>0.002757489855299861</v>
@@ -7757,16 +7757,16 @@
         <v>5.276943263115948e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.103014305314398e-05</v>
+        <v>5.103014305314399e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.957739802512062e-07</v>
+        <v>8.957739802512064e-07</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.2027579446795142</v>
+        <v>0.2027579446795143</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.00688902169448204</v>
+        <v>0.006889021694482041</v>
       </c>
       <c r="BI7" t="n">
         <v>1.515907564245401e-05</v>
@@ -7778,13 +7778,13 @@
         <v>0.0003844410749037022</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0003197640840361225</v>
+        <v>0.0003197640840361226</v>
       </c>
       <c r="BM7" t="n">
         <v>0.0121173169853903</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0003112443166411098</v>
+        <v>0.0003112443166411099</v>
       </c>
       <c r="BO7" t="n">
         <v>0.0001035245270920986</v>
@@ -7793,10 +7793,10 @@
         <v>5.503616093316101e-06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.001454720997672873</v>
+        <v>0.001454720997672874</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0009033309252684605</v>
+        <v>0.0009033309252684606</v>
       </c>
       <c r="BS7" t="n">
         <v>0.001265869640255276</v>
@@ -7811,22 +7811,22 @@
         <v>0.00688902169448204</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.06030483164398771</v>
+        <v>0.06030483164398766</v>
       </c>
       <c r="BX7" t="n">
         <v>5.65635584027005e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.3972906853462294</v>
+        <v>0.3972906853462295</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.802373587400289e-07</v>
+        <v>3.802373587400288e-07</v>
       </c>
       <c r="CA7" t="n">
         <v>0.0002019428046604986</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.03721992794981973</v>
+        <v>0.03721992794981974</v>
       </c>
       <c r="CC7" t="n">
         <v>0.0002101087780189975</v>
@@ -7835,16 +7835,16 @@
         <v>8.899265664792021e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0003906329300695459</v>
+        <v>0.000390632930069546</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0002278731397524993</v>
+        <v>0.0002278731397524994</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.06409543254386778</v>
+        <v>0.06409543254386782</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0005712101222630879</v>
+        <v>0.0005712101222630878</v>
       </c>
       <c r="CI7" t="n">
         <v>0.01639134824370144</v>
@@ -7862,13 +7862,13 @@
         <v>3.766112552267128e-05</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0004003927998928637</v>
+        <v>0.0004003927998928638</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.002960314198879891</v>
+        <v>0.00296031419887989</v>
       </c>
       <c r="CP7" t="n">
-        <v>5.382049459993215e-05</v>
+        <v>5.382049459993216e-05</v>
       </c>
       <c r="CQ7" t="n">
         <v>0.001931963071480932</v>
@@ -7877,31 +7877,31 @@
         <v>0.0002814552108602311</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0008067035989224396</v>
+        <v>0.0008067035989224398</v>
       </c>
       <c r="CT7" t="n">
         <v>1.068212250185585e-05</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0002223832717431476</v>
+        <v>0.0002223832717431477</v>
       </c>
       <c r="CV7" t="n">
-        <v>3.141599174294617e-14</v>
+        <v>3.141599174294604e-14</v>
       </c>
       <c r="CW7" t="n">
-        <v>8.558841439502641e-05</v>
+        <v>8.558841439502643e-05</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0006698364148566628</v>
+        <v>0.0006698364148566634</v>
       </c>
       <c r="CY7" t="n">
-        <v>5.077344082320992e-05</v>
+        <v>5.077344082320994e-05</v>
       </c>
       <c r="CZ7" t="n">
-        <v>9.164738614382468e-08</v>
+        <v>9.164738614382471e-08</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.976685307582819e-13</v>
+        <v>2.97668530758282e-13</v>
       </c>
       <c r="DB7" t="n">
         <v>2.077181569953612e-13</v>
@@ -7916,22 +7916,22 @@
         <v>1.883591186408195e-13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.942484274114513e-13</v>
+        <v>1.942484274114512e-13</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.103733313959208e-22</v>
+        <v>3.103733313959207e-22</v>
       </c>
       <c r="DH7" t="n">
         <v>2.19982477513284e-22</v>
       </c>
       <c r="DI7" t="n">
-        <v>1.871935742951584e-22</v>
+        <v>1.871935742951585e-22</v>
       </c>
       <c r="DJ7" t="n">
-        <v>9.559231493551267e-23</v>
+        <v>9.55923149355126e-23</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.005300005646235e-22</v>
+        <v>2.005300005646236e-22</v>
       </c>
       <c r="DL7" t="n">
         <v>2.064505106977253e-22</v>
@@ -7949,10 +7949,10 @@
         <v>1.206505910401974e-13</v>
       </c>
       <c r="DQ7" t="n">
-        <v>3.309504507701856e-13</v>
+        <v>3.309504507701855e-13</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.664799007133015e-13</v>
+        <v>2.664799007133014e-13</v>
       </c>
       <c r="DS7" t="n">
         <v>3.100789162230691e-13</v>
@@ -7961,13 +7961,13 @@
         <v>2.366727240812287e-13</v>
       </c>
       <c r="DU7" t="n">
-        <v>2.317833887364202e-13</v>
+        <v>2.317833887364203e-13</v>
       </c>
       <c r="DV7" t="n">
         <v>2.195919723802235e-13</v>
       </c>
       <c r="DW7" t="n">
-        <v>1.240684753475922e-13</v>
+        <v>1.240684753475921e-13</v>
       </c>
       <c r="DX7" t="n">
         <v>1.065139056413605e-13</v>
@@ -7985,7 +7985,7 @@
         <v>2.407623374081901e-13</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.077450637127649e-13</v>
+        <v>2.077450637127651e-13</v>
       </c>
       <c r="ED7" t="n">
         <v>1.158516537064861e-13</v>
@@ -7997,7 +7997,7 @@
         <v>0.4048438996336426</v>
       </c>
       <c r="EG7" t="n">
-        <v>2.613105506326317</v>
+        <v>2.613105506326324</v>
       </c>
     </row>
     <row r="8">
@@ -8015,76 +8015,76 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.382886989749878</v>
+        <v>4.382886989749879</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00749849326846003</v>
+        <v>0.00749849326846005</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01306813215378867</v>
+        <v>0.01306813215378869</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02851613131997464</v>
+        <v>0.0285161313199747</v>
       </c>
       <c r="H8" t="n">
-        <v>3.496431614450212e-05</v>
+        <v>3.4964316144502e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009136096282307255</v>
+        <v>0.0009136096282307264</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001900083916865151</v>
+        <v>0.0001900083916865155</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001025409916909158</v>
+        <v>0.001025409916909157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004799121389144084</v>
+        <v>0.0004799121389144081</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003097472200252493</v>
+        <v>0.003097472200252489</v>
       </c>
       <c r="N8" t="n">
-        <v>2.955270057943437e-05</v>
+        <v>2.955270057943436e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.047117716638697e-05</v>
+        <v>6.047117716638711e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003483560681771163</v>
+        <v>0.003483560681771167</v>
       </c>
       <c r="Q8" t="n">
         <v>2.574113704615097e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.671763139103716e-07</v>
+        <v>4.671763139103717e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.673451196834198e-05</v>
+        <v>5.673451196834197e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>5.03626604061551e-07</v>
+        <v>5.036266040615513e-07</v>
       </c>
       <c r="U8" t="n">
         <v>1.599619440900955e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0005054999524944441</v>
+        <v>0.0005054999524944435</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001711175767204621</v>
+        <v>0.001711175767205505</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004501520456296311</v>
+        <v>0.004501520456296312</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001878271795660551</v>
+        <v>0.0001878271795660578</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.06849969317789747</v>
+        <v>-0.06849969317789749</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.041681317768654e-16</v>
+        <v>2.041681317768657e-16</v>
       </c>
       <c r="AB8" t="n">
         <v>0.004221996998476449</v>
@@ -8096,13 +8096,13 @@
         <v>0.00162620467462924</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001853977632083819</v>
+        <v>0.001853977632083818</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.3063780284810722</v>
+        <v>0.3063780284810723</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0003477916658826165</v>
+        <v>0.0003477916658826166</v>
       </c>
       <c r="AH8" t="n">
         <v>0.0009616106877824066</v>
@@ -8120,7 +8120,7 @@
         <v>4.836080786074755e-06</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0004849401812181444</v>
+        <v>0.0004849401812181443</v>
       </c>
       <c r="AN8" t="n">
         <v>1.956452121796353e-05</v>
@@ -8129,7 +8129,7 @@
         <v>0.1105267675102022</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.002742229568024959</v>
+        <v>0.002742229568024958</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.002373250792261879</v>
@@ -8138,7 +8138,7 @@
         <v>0.00333130921529482</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.589263209972391e-14</v>
+        <v>3.589263209972393e-14</v>
       </c>
       <c r="AT8" t="n">
         <v>0.003027180651909464</v>
@@ -8159,16 +8159,16 @@
         <v>0.001775100528543945</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0003080732546043976</v>
+        <v>0.0003080732546043975</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0004773040518682272</v>
+        <v>0.0004773040518682271</v>
       </c>
       <c r="BB8" t="n">
         <v>0.002837845121754673</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0005718805881234146</v>
+        <v>0.0005718805881234145</v>
       </c>
       <c r="BD8" t="n">
         <v>5.348364817883251e-05</v>
@@ -8177,13 +8177,13 @@
         <v>5.281773228086631e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.394933479318015e-07</v>
+        <v>9.394933479318016e-07</v>
       </c>
       <c r="BG8" t="n">
         <v>0.2098988700422701</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.006926401009759983</v>
+        <v>0.006926401009759986</v>
       </c>
       <c r="BI8" t="n">
         <v>1.53722565601733e-05</v>
@@ -8192,28 +8192,28 @@
         <v>0.0536555848563832</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0003949129285156392</v>
+        <v>0.0003949129285156391</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0003215382781631339</v>
+        <v>0.0003215382781631338</v>
       </c>
       <c r="BM8" t="n">
         <v>0.01233421558459751</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0003223766255323614</v>
+        <v>0.0003223766255323615</v>
       </c>
       <c r="BO8" t="n">
         <v>0.0001071849920780399</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.645239495259087e-06</v>
+        <v>5.645239495259086e-06</v>
       </c>
       <c r="BQ8" t="n">
         <v>0.001507792482519305</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0009350172321635655</v>
+        <v>0.0009350172321635654</v>
       </c>
       <c r="BS8" t="n">
         <v>0.001281783509023476</v>
@@ -8225,16 +8225,16 @@
         <v>0.009734670319730203</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.006926401009759983</v>
+        <v>0.006926401009759985</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.06128231566504648</v>
+        <v>0.06128231566504642</v>
       </c>
       <c r="BX8" t="n">
         <v>5.928600820494404e-05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.4050061725484237</v>
+        <v>0.4050061725484239</v>
       </c>
       <c r="BZ8" t="n">
         <v>3.901230915870707e-07</v>
@@ -8249,7 +8249,7 @@
         <v>0.000216324132907101</v>
       </c>
       <c r="CD8" t="n">
-        <v>9.152879637000319e-05</v>
+        <v>9.152879637000321e-05</v>
       </c>
       <c r="CE8" t="n">
         <v>0.0004053659469900521</v>
@@ -8258,13 +8258,13 @@
         <v>0.0002348811299335079</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.06582523563083929</v>
+        <v>0.06582523563083927</v>
       </c>
       <c r="CH8" t="n">
         <v>0.0005873048864501139</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0169060001727936</v>
+        <v>0.01690600017279359</v>
       </c>
       <c r="CJ8" t="n">
         <v>0.0002291240509716556</v>
@@ -8279,7 +8279,7 @@
         <v>3.885288509476002e-05</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.000422803814353999</v>
+        <v>0.0004228038143539992</v>
       </c>
       <c r="CO8" t="n">
         <v>0.003006192286215968</v>
@@ -8291,25 +8291,25 @@
         <v>0.001989099396292556</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0002895105274935052</v>
+        <v>0.0002895105274935053</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.000833472299758456</v>
+        <v>0.0008334722997584558</v>
       </c>
       <c r="CT8" t="n">
         <v>1.086546299938839e-05</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0002358970739205748</v>
+        <v>0.0002358970739205749</v>
       </c>
       <c r="CV8" t="n">
-        <v>3.568846453613832e-14</v>
+        <v>3.568846453613831e-14</v>
       </c>
       <c r="CW8" t="n">
         <v>8.815202594313344e-05</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0006912019636143735</v>
+        <v>0.0006912019636143734</v>
       </c>
       <c r="CY8" t="n">
         <v>5.287060327107332e-05</v>
@@ -8327,7 +8327,7 @@
         <v>1.816250023193646e-13</v>
       </c>
       <c r="DD8" t="n">
-        <v>8.744358801837004e-14</v>
+        <v>8.744358801837001e-14</v>
       </c>
       <c r="DE8" t="n">
         <v>1.947308564878536e-13</v>
@@ -8339,25 +8339,25 @@
         <v>3.172403576693008e-22</v>
       </c>
       <c r="DH8" t="n">
-        <v>2.272874458441179e-22</v>
+        <v>2.27287445844118e-22</v>
       </c>
       <c r="DI8" t="n">
-        <v>1.935178660520861e-22</v>
+        <v>1.935178660520862e-22</v>
       </c>
       <c r="DJ8" t="n">
-        <v>9.907538588867725e-23</v>
+        <v>9.90753858886772e-23</v>
       </c>
       <c r="DK8" t="n">
         <v>2.071527056822669e-22</v>
       </c>
       <c r="DL8" t="n">
-        <v>2.132633886567222e-22</v>
+        <v>2.132633886567221e-22</v>
       </c>
       <c r="DM8" t="n">
         <v>1.99862397419282e-13</v>
       </c>
       <c r="DN8" t="n">
-        <v>2.823109543738638e-13</v>
+        <v>2.823109543738639e-13</v>
       </c>
       <c r="DO8" t="n">
         <v>2.860272064549586e-13</v>
@@ -8366,7 +8366,7 @@
         <v>1.231770259861532e-13</v>
       </c>
       <c r="DQ8" t="n">
-        <v>3.354250930080514e-13</v>
+        <v>3.354250930080515e-13</v>
       </c>
       <c r="DR8" t="n">
         <v>2.766365301609252e-13</v>
@@ -8390,22 +8390,22 @@
         <v>1.087889816906689e-13</v>
       </c>
       <c r="DY8" t="n">
-        <v>2.346740532118281e-13</v>
+        <v>2.346740532118282e-13</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.285399474572236e-13</v>
+        <v>2.285399474572237e-13</v>
       </c>
       <c r="EA8" t="n">
-        <v>3.390328340340983e-13</v>
+        <v>3.390328340340981e-13</v>
       </c>
       <c r="EB8" t="n">
         <v>2.487487380251612e-13</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.147427435658498e-13</v>
+        <v>2.147427435658501e-13</v>
       </c>
       <c r="ED8" t="n">
-        <v>1.20000844605827e-13</v>
+        <v>1.200008446058271e-13</v>
       </c>
       <c r="EE8" t="n">
         <v>5.986392650717769e-12</v>
@@ -8414,7 +8414,7 @@
         <v>0.4097995632622788</v>
       </c>
       <c r="EG8" t="n">
-        <v>2.613105366059148</v>
+        <v>2.613105366059149</v>
       </c>
     </row>
     <row r="9">
@@ -8432,79 +8432,79 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.31237394635549</v>
+        <v>4.312373946355489</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001068572861543728</v>
+        <v>0.001068572861543629</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01051862546047665</v>
+        <v>0.01051862546047664</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02194270039317896</v>
+        <v>0.02194270039317889</v>
       </c>
       <c r="H9" t="n">
-        <v>3.365050095597088e-05</v>
+        <v>3.365050095597067e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000881032489916614</v>
+        <v>0.000881032489916618</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001781312359758857</v>
+        <v>0.0001781312359758847</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0007563109193431276</v>
+        <v>0.0007563109193431231</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004471238191749837</v>
+        <v>0.0004471238191749831</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002548308545974136</v>
+        <v>0.002548308545974131</v>
       </c>
       <c r="N9" t="n">
         <v>2.82061227066911e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.792042470899467e-05</v>
+        <v>4.792042470899435e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00314072711154491</v>
+        <v>0.003140727111544897</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.032112541396132e-05</v>
+        <v>2.032112541396057e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.624448121493107e-07</v>
+        <v>4.624448121493108e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>5.554068862200804e-05</v>
+        <v>5.554068862200802e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.779091009372072e-07</v>
+        <v>3.779091009372067e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>1.376672899923711e-06</v>
+        <v>1.376672899923708e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0004217603311659523</v>
+        <v>0.0004217603311659481</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001395027985648584</v>
+        <v>0.001395027985648409</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004462952142155598</v>
+        <v>0.0044629521421556</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0001552812779334231</v>
+        <v>0.0001552812779334222</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.008079364413351484</v>
+        <v>-0.008079364413350823</v>
       </c>
       <c r="AA9" t="n">
         <v>1.935012500718561e-16</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00411331201178214</v>
+        <v>0.004113312011782139</v>
       </c>
       <c r="AC9" t="n">
         <v>0.01320134159809399</v>
@@ -8513,19 +8513,19 @@
         <v>0.001572905627109097</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001806001209352579</v>
+        <v>0.001806001209352578</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2968332698715988</v>
+        <v>0.2968332698715987</v>
       </c>
       <c r="AG9" t="n">
         <v>0.0003374527678039616</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0009374611539899725</v>
+        <v>0.000937461153989972</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.685590841604038e-07</v>
+        <v>3.685590841604037e-07</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.0001038825198989454</v>
@@ -8534,169 +8534,169 @@
         <v>0.002853279599369856</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.711587714176117e-06</v>
+        <v>4.711587714176115e-06</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0004692647978410094</v>
+        <v>0.0004692647978410092</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.909792721146772e-05</v>
+        <v>1.909792721146771e-05</v>
       </c>
       <c r="AO9" t="n">
         <v>0.1105267675102022</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.006075761293592949</v>
+        <v>-0.006075761293592962</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.002311501821709342</v>
+        <v>0.002311501821709341</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.003286165054809187</v>
+        <v>0.003286165054809186</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.114725066646859e-14</v>
+        <v>3.114725066646854e-14</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.002941566743009439</v>
+        <v>0.002941566743009438</v>
       </c>
       <c r="AU9" t="n">
         <v>1.016879648027142e-06</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.900374713439689e-06</v>
+        <v>1.900374713439688e-06</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.272532915908398e-06</v>
+        <v>2.272532915908397e-06</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0001646591524460763</v>
+        <v>0.0001646591524460762</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001728863173061416</v>
+        <v>0.001728863173061415</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.0002990959769339638</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0004561280789809186</v>
+        <v>0.0004561280789809185</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.002764716455935804</v>
+        <v>0.002764716455935803</v>
       </c>
       <c r="BC9" t="n">
         <v>0.0005566925176788471</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.284360720258805e-05</v>
+        <v>5.284360720258804e-05</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.108662495676156e-05</v>
+        <v>5.108662495676155e-05</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.961003450428491e-07</v>
+        <v>8.961003450428489e-07</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.2011730511268595</v>
+        <v>0.2011730511268593</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.006888153992037419</v>
+        <v>0.006888153992037418</v>
       </c>
       <c r="BI9" t="n">
         <v>1.518216531260726e-05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0530210014858625</v>
+        <v>0.05302100148586251</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0003853602321557287</v>
+        <v>0.0003853602321557286</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0003197850201634382</v>
+        <v>0.0003197850201634383</v>
       </c>
       <c r="BM9" t="n">
         <v>0.01212224382185751</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0003113722841029423</v>
+        <v>0.0003113722841029422</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.000103585762563022</v>
+        <v>0.0001035857625630219</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.507550688168881e-06</v>
+        <v>5.507550688168879e-06</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001456872042577888</v>
+        <v>0.001456872042577887</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0009069835744287899</v>
+        <v>0.0009069835744287898</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.00126463053182443</v>
+        <v>0.001264630531824429</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0007165162740867934</v>
+        <v>0.0007165162740867928</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.009484836436077407</v>
+        <v>0.009484836436077403</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.006888153992037416</v>
+        <v>0.006888153992037417</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.05997343763650246</v>
+        <v>0.05997343763650247</v>
       </c>
       <c r="BX9" t="n">
-        <v>5.657964287112529e-05</v>
+        <v>5.657964287112527e-05</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.3633958824189311</v>
+        <v>0.3633958824189308</v>
       </c>
       <c r="BZ9" t="n">
         <v>3.80542751143553e-07</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0002021993233855334</v>
+        <v>0.0002021993233855333</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0370192773567766</v>
+        <v>0.03701927735677658</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0002100482149163176</v>
+        <v>0.0002100482149163175</v>
       </c>
       <c r="CD9" t="n">
         <v>8.894060750290611e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0003913339235566124</v>
+        <v>0.0003913339235566125</v>
       </c>
       <c r="CF9" t="n">
         <v>0.0002278758566711198</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0627999259563676</v>
+        <v>0.06279992595636759</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0005723440246383315</v>
+        <v>0.0005723440246383314</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01623258830126614</v>
+        <v>0.01623258830126613</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0002232782213154515</v>
+        <v>0.0002232782213154514</v>
       </c>
       <c r="CK9" t="n">
         <v>0.000391664382795653</v>
       </c>
       <c r="CL9" t="n">
-        <v>5.408298076014175e-05</v>
+        <v>5.408298076014174e-05</v>
       </c>
       <c r="CM9" t="n">
         <v>3.767016061211029e-05</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0004008217051435377</v>
+        <v>0.0004008217051435376</v>
       </c>
       <c r="CO9" t="n">
         <v>0.002963328830245846</v>
@@ -8705,43 +8705,43 @@
         <v>5.381009620529289e-05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001937626351613083</v>
+        <v>0.001937626351613082</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0002820878495864404</v>
+        <v>0.0002820878495864402</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0008072149250971141</v>
+        <v>0.0008072149250971138</v>
       </c>
       <c r="CT9" t="n">
         <v>1.068696597974795e-05</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0002227792720262313</v>
+        <v>0.0002227792720262312</v>
       </c>
       <c r="CV9" t="n">
-        <v>3.09537499095041e-14</v>
+        <v>3.095374990950408e-14</v>
       </c>
       <c r="CW9" t="n">
-        <v>8.557187827591323e-05</v>
+        <v>8.557187827591322e-05</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0006717125678369181</v>
+        <v>0.0006717125678369187</v>
       </c>
       <c r="CY9" t="n">
-        <v>5.091201629295208e-05</v>
+        <v>5.091201629295207e-05</v>
       </c>
       <c r="CZ9" t="n">
-        <v>9.16847384494402e-08</v>
+        <v>9.168473844944015e-08</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.974927321384814e-13</v>
+        <v>2.974927321384813e-13</v>
       </c>
       <c r="DB9" t="n">
         <v>2.081395619237487e-13</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.762302832681873e-13</v>
+        <v>1.762302832681874e-13</v>
       </c>
       <c r="DD9" t="n">
         <v>8.451484914479023e-14</v>
@@ -8753,22 +8753,22 @@
         <v>1.946071274878458e-13</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.102096817526186e-22</v>
+        <v>3.102096817526185e-22</v>
       </c>
       <c r="DH9" t="n">
-        <v>2.204189558783965e-22</v>
+        <v>2.204189558783966e-22</v>
       </c>
       <c r="DI9" t="n">
-        <v>1.879044060656086e-22</v>
+        <v>1.879044060656085e-22</v>
       </c>
       <c r="DJ9" t="n">
-        <v>9.592869693950148e-23</v>
+        <v>9.592869693950146e-23</v>
       </c>
       <c r="DK9" t="n">
         <v>2.011162603521479e-22</v>
       </c>
       <c r="DL9" t="n">
-        <v>2.068242199051219e-22</v>
+        <v>2.068242199051218e-22</v>
       </c>
       <c r="DM9" t="n">
         <v>1.911184727972967e-13</v>
@@ -8777,7 +8777,7 @@
         <v>2.787506948920704e-13</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.7840318464486e-13</v>
+        <v>2.784031846448599e-13</v>
       </c>
       <c r="DP9" t="n">
         <v>1.207960786539824e-13</v>
@@ -8786,16 +8786,16 @@
         <v>3.313339956645026e-13</v>
       </c>
       <c r="DR9" t="n">
-        <v>2.673398968798379e-13</v>
+        <v>2.673398968798377e-13</v>
       </c>
       <c r="DS9" t="n">
         <v>3.104836124548075e-13</v>
       </c>
       <c r="DT9" t="n">
-        <v>2.375564017940542e-13</v>
+        <v>2.375564017940541e-13</v>
       </c>
       <c r="DU9" t="n">
-        <v>2.320866816829797e-13</v>
+        <v>2.320866816829796e-13</v>
       </c>
       <c r="DV9" t="n">
         <v>2.200043952364425e-13</v>
@@ -8807,28 +8807,28 @@
         <v>1.066774092987334e-13</v>
       </c>
       <c r="DY9" t="n">
-        <v>2.276160279062434e-13</v>
+        <v>2.276160279062433e-13</v>
       </c>
       <c r="DZ9" t="n">
         <v>2.21886308179724e-13</v>
       </c>
       <c r="EA9" t="n">
-        <v>3.313811722445834e-13</v>
+        <v>3.313811722445833e-13</v>
       </c>
       <c r="EB9" t="n">
-        <v>2.412598593148234e-13</v>
+        <v>2.412598593148235e-13</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.085172459777854e-13</v>
+        <v>2.085172459777852e-13</v>
       </c>
       <c r="ED9" t="n">
-        <v>1.162484769034096e-13</v>
+        <v>1.162484769034097e-13</v>
       </c>
       <c r="EE9" t="n">
         <v>5.986392650717769e-12</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.3734932901144836</v>
+        <v>0.3734932901144833</v>
       </c>
       <c r="EG9" t="n">
         <v>2.613105459650757</v>
@@ -8849,97 +8849,97 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.114621227939415</v>
+        <v>4.114621227939411</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0006555280838737802</v>
+        <v>0.0006555280838737792</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009227806474251426</v>
+        <v>0.00922780647425143</v>
       </c>
       <c r="G10" t="n">
         <v>0.01914839970242504</v>
       </c>
       <c r="H10" t="n">
-        <v>3.274896862308848e-05</v>
+        <v>3.274896862308797e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008601806002358269</v>
+        <v>0.0008601806002358249</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001700539907640886</v>
+        <v>0.0001700539907640877</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0006328263258109277</v>
+        <v>0.0006328263258109261</v>
       </c>
       <c r="L10" t="n">
-        <v>0.000436893486675964</v>
+        <v>0.0004368934866759642</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00220182944509666</v>
+        <v>0.002201829445096656</v>
       </c>
       <c r="N10" t="n">
-        <v>2.722379056363304e-05</v>
+        <v>2.722379056363303e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>4.329042340711879e-05</v>
+        <v>4.329042340711881e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002859267554310283</v>
+        <v>0.002859267554310285</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.490704148805639e-05</v>
+        <v>1.490704148805472e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.582267167656856e-07</v>
+        <v>4.582267167656855e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.451536044885216e-05</v>
+        <v>5.451536044885213e-05</v>
       </c>
       <c r="T10" t="n">
         <v>2.250447543493167e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>1.277164594051204e-06</v>
+        <v>1.277164594051203e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0003902762579412793</v>
+        <v>0.00039027625794128</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001272428801061377</v>
+        <v>0.001272428801062099</v>
       </c>
       <c r="X10" t="n">
         <v>0.00441971449285951</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0001356977020902577</v>
+        <v>0.000135697702090259</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.004785632619567455</v>
+        <v>-0.004785632619567447</v>
       </c>
       <c r="AA10" t="n">
         <v>1.872638433949558e-16</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.004001272609631957</v>
+        <v>0.004001272609631958</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01284165970274805</v>
+        <v>0.01284165970274804</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.001520381677929402</v>
+        <v>0.001520381677929403</v>
       </c>
       <c r="AE10" t="n">
         <v>0.001756785781808004</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2856471116369296</v>
+        <v>0.2856471116369295</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0003254760720414828</v>
+        <v>0.0003254760720414829</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0009124108182427813</v>
+        <v>0.0009124108182427811</v>
       </c>
       <c r="AI10" t="n">
         <v>3.509314423397539e-07</v>
@@ -8951,10 +8951,10 @@
         <v>0.002775568384200631</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.583252331603052e-06</v>
+        <v>4.583252331603053e-06</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0004537787659289906</v>
+        <v>0.0004537787659289904</v>
       </c>
       <c r="AN10" t="n">
         <v>1.866438501751017e-05</v>
@@ -8963,19 +8963,19 @@
         <v>0.1105267675102022</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.02964874380351462</v>
+        <v>-0.02964874380351464</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.00224848001791191</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.003243045426902212</v>
+        <v>0.003243045426902213</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.943135247953929e-14</v>
+        <v>2.94313524795393e-14</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0028556915682692</v>
+        <v>0.002855691568269199</v>
       </c>
       <c r="AU10" t="n">
         <v>9.861338491338444e-07</v>
@@ -8987,31 +8987,31 @@
         <v>2.164735458789214e-06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0001595471741174202</v>
+        <v>0.0001595471741174201</v>
       </c>
       <c r="AY10" t="n">
         <v>0.0016817219274938</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0002908842463573326</v>
+        <v>0.0002908842463573327</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0004376377005960085</v>
+        <v>0.0004376377005960088</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.002689403475706803</v>
+        <v>0.002689403475706802</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0005426061450105636</v>
+        <v>0.0005426061450105639</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.219408392289888e-05</v>
+        <v>5.219408392289889e-05</v>
       </c>
       <c r="BE10" t="n">
         <v>4.938069216159272e-05</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.582641469050579e-07</v>
+        <v>8.582641469050581e-07</v>
       </c>
       <c r="BG10" t="n">
         <v>0.1908548694206174</v>
@@ -9023,10 +9023,10 @@
         <v>1.498769224879055e-05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.05298624415383535</v>
+        <v>0.05298624415383532</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0003765897530283166</v>
+        <v>0.0003765897530283164</v>
       </c>
       <c r="BL10" t="n">
         <v>0.000318585913216377</v>
@@ -9038,40 +9038,40 @@
         <v>0.0003018109565640544</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0001004429789523522</v>
+        <v>0.0001004429789523521</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.379675270639068e-06</v>
+        <v>5.379675270639067e-06</v>
       </c>
       <c r="BQ10" t="n">
         <v>0.001406957457863772</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0008791036233095942</v>
+        <v>0.000879103623309594</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.001264571345906443</v>
+        <v>0.001264571345906442</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0006780628393597269</v>
+        <v>0.0006780628393597268</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.009226556471993769</v>
+        <v>0.009226556471993771</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.006861288733411182</v>
+        <v>0.006861288733411183</v>
       </c>
       <c r="BW10" t="n">
         <v>0.05858578206573892</v>
       </c>
       <c r="BX10" t="n">
-        <v>5.421869757726574e-05</v>
+        <v>5.421869757726572e-05</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.2846994989877362</v>
+        <v>0.2846994989877359</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.716464741223737e-07</v>
+        <v>3.716464741223736e-07</v>
       </c>
       <c r="CA10" t="n">
         <v>0.0001925284255506921</v>
@@ -9080,7 +9080,7 @@
         <v>0.03611081951542283</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0002037197724544927</v>
+        <v>0.0002037197724544926</v>
       </c>
       <c r="CD10" t="n">
         <v>8.641523342490669e-05</v>
@@ -9092,31 +9092,31 @@
         <v>0.0002208500626064248</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.06190354868319575</v>
+        <v>0.06190354868319574</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0005568393991096308</v>
+        <v>0.0005568393991096307</v>
       </c>
       <c r="CI10" t="n">
         <v>0.01581322245774724</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0002172013559057779</v>
+        <v>0.0002172013559057778</v>
       </c>
       <c r="CK10" t="n">
         <v>0.0003868502690756038</v>
       </c>
       <c r="CL10" t="n">
-        <v>5.338402564417573e-05</v>
+        <v>5.338402564417574e-05</v>
       </c>
       <c r="CM10" t="n">
         <v>3.648861935112757e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0003816501122797113</v>
+        <v>0.0003816501122797112</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.002923834818750892</v>
+        <v>0.002923834818750893</v>
       </c>
       <c r="CP10" t="n">
         <v>5.217689498913881e-05</v>
@@ -9128,58 +9128,58 @@
         <v>0.0002744070487235073</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0007811522191273023</v>
+        <v>0.0007811522191273025</v>
       </c>
       <c r="CT10" t="n">
         <v>1.053785454230258e-05</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0002114214218855199</v>
+        <v>0.0002114214218855198</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.924408910209648e-14</v>
+        <v>2.924408910209647e-14</v>
       </c>
       <c r="CW10" t="n">
-        <v>8.297466872743708e-05</v>
+        <v>8.29746687274371e-05</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0006539324846730392</v>
+        <v>0.000653932484673039</v>
       </c>
       <c r="CY10" t="n">
-        <v>4.897555069560718e-05</v>
+        <v>4.897555069560717e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>8.883831060707936e-08</v>
+        <v>8.883831060707938e-08</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.923966635052872e-13</v>
+        <v>2.923966635052871e-13</v>
       </c>
       <c r="DB10" t="n">
-        <v>2.029669100190632e-13</v>
+        <v>2.029669100190633e-13</v>
       </c>
       <c r="DC10" t="n">
         <v>1.708169793780163e-13</v>
       </c>
       <c r="DD10" t="n">
-        <v>8.164054385566534e-14</v>
+        <v>8.164054385566531e-14</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.83654799511718e-13</v>
+        <v>1.836547995117179e-13</v>
       </c>
       <c r="DF10" t="n">
         <v>1.894459815167181e-13</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.048675829146999e-22</v>
+        <v>3.048675829147002e-22</v>
       </c>
       <c r="DH10" t="n">
-        <v>2.14999898746547e-22</v>
+        <v>2.149998987465471e-22</v>
       </c>
       <c r="DI10" t="n">
-        <v>1.822598586653181e-22</v>
+        <v>1.822598586653183e-22</v>
       </c>
       <c r="DJ10" t="n">
-        <v>9.282446294133733e-23</v>
+        <v>9.282446294133741e-23</v>
       </c>
       <c r="DK10" t="n">
         <v>1.955945794471718e-22</v>
@@ -9191,64 +9191,64 @@
         <v>1.860535142986129e-13</v>
       </c>
       <c r="DN10" t="n">
-        <v>2.760234279479905e-13</v>
+        <v>2.760234279479904e-13</v>
       </c>
       <c r="DO10" t="n">
         <v>2.729122126897659e-13</v>
       </c>
       <c r="DP10" t="n">
-        <v>1.188271063601147e-13</v>
+        <v>1.188271063601146e-13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>3.275817504114591e-13</v>
+        <v>3.275817504114593e-13</v>
       </c>
       <c r="DR10" t="n">
         <v>2.590155744897928e-13</v>
       </c>
       <c r="DS10" t="n">
-        <v>3.069335682788479e-13</v>
+        <v>3.069335682788478e-13</v>
       </c>
       <c r="DT10" t="n">
         <v>2.296033291702426e-13</v>
       </c>
       <c r="DU10" t="n">
-        <v>2.297992185478041e-13</v>
+        <v>2.297992185478042e-13</v>
       </c>
       <c r="DV10" t="n">
-        <v>2.151494359635737e-13</v>
+        <v>2.151494359635736e-13</v>
       </c>
       <c r="DW10" t="n">
         <v>1.200433810421179e-13</v>
       </c>
       <c r="DX10" t="n">
-        <v>1.04847458145672e-13</v>
+        <v>1.048474581456721e-13</v>
       </c>
       <c r="DY10" t="n">
         <v>2.215641652869935e-13</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2.157202576946475e-13</v>
+        <v>2.157202576946474e-13</v>
       </c>
       <c r="EA10" t="n">
         <v>3.253952486428406e-13</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.351966940779076e-13</v>
+        <v>2.351966940779077e-13</v>
       </c>
       <c r="EC10" t="n">
         <v>2.022317033759314e-13</v>
       </c>
       <c r="ED10" t="n">
-        <v>1.125099174653633e-13</v>
+        <v>1.125099174653634e-13</v>
       </c>
       <c r="EE10" t="n">
         <v>5.986392650717769e-12</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3073319159288185</v>
+        <v>0.3073319159288186</v>
       </c>
       <c r="EG10" t="n">
-        <v>2.613105306302199</v>
+        <v>2.613105306302194</v>
       </c>
     </row>
   </sheetData>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.053911307798263</v>
+        <v>2.053911307798265</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3186169771741244</v>
+        <v>0.3186169771741251</v>
       </c>
       <c r="F2" t="n">
         <v>0.03621468244334192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01557196564824552</v>
+        <v>0.01557196564824549</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1009667770899313</v>
+        <v>0.1009667770899311</v>
       </c>
       <c r="I2" t="n">
         <v>4.075563172662792e-06</v>
@@ -9366,7 +9366,7 @@
         <v>0.004377135599824692</v>
       </c>
       <c r="L2" t="n">
-        <v>1.576884470090241</v>
+        <v>1.576884470090243</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -9387,31 +9387,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.80990747878584</v>
+        <v>1.809907478785838</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3039913892363109</v>
+        <v>0.3039913892363106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02443314372181957</v>
+        <v>0.02443314372181959</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01538132220463726</v>
+        <v>0.01538132220463733</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09950266143646799</v>
+        <v>0.09950266143646809</v>
       </c>
       <c r="I3" t="n">
-        <v>3.590227273927664e-06</v>
+        <v>3.590227273927669e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001112433618232633</v>
+        <v>0.00111243361823263</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003813720819753734</v>
+        <v>0.003813720819757487</v>
       </c>
       <c r="L3" t="n">
-        <v>1.361669215649089</v>
+        <v>1.36166921564909</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -9432,31 +9432,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.698428342207857</v>
+        <v>1.698428342207856</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2927033980521497</v>
+        <v>0.2927033980521493</v>
       </c>
       <c r="F4" t="n">
         <v>0.01533339641248511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01524914431042959</v>
+        <v>0.01524914431042958</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09854457734191194</v>
+        <v>0.09854457734191198</v>
       </c>
       <c r="I4" t="n">
-        <v>3.216532531912033e-06</v>
+        <v>3.216532531912038e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009917168601908375</v>
+        <v>0.0009917168601908393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003398117346378841</v>
+        <v>0.003398117346378847</v>
       </c>
       <c r="L4" t="n">
-        <v>1.272204773413052</v>
+        <v>1.272204773413049</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -9477,31 +9477,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.837711780014038</v>
+        <v>1.837711780014041</v>
       </c>
       <c r="E5" t="n">
         <v>0.2965067861671022</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01996172491239409</v>
+        <v>0.01996172491239408</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01528541971022187</v>
+        <v>0.01528541971022184</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0990493921303197</v>
+        <v>0.09904939213031982</v>
       </c>
       <c r="I5" t="n">
-        <v>3.315461137385448e-06</v>
+        <v>3.315461137385454e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001078867357490454</v>
+        <v>0.001078867357490453</v>
       </c>
       <c r="K5" t="n">
         <v>0.003708296314999622</v>
       </c>
       <c r="L5" t="n">
-        <v>1.402118010141696</v>
+        <v>1.402118010141699</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -9531,22 +9531,22 @@
         <v>0.01272660826062423</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01512528837100167</v>
+        <v>0.0151252883710017</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09666441312259548</v>
+        <v>0.09666441312259549</v>
       </c>
       <c r="I6" t="n">
-        <v>2.761299622841463e-06</v>
+        <v>2.761299622839766e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008569489994980376</v>
+        <v>0.0008569489994980367</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00285867894652403</v>
+        <v>0.002858678946524017</v>
       </c>
       <c r="L6" t="n">
-        <v>1.088035139495924</v>
+        <v>1.088035139495923</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -9570,28 +9570,28 @@
         <v>1.349844878288684</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2692748218174132</v>
+        <v>0.2692748218174136</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01130415107891838</v>
+        <v>0.01130415107891832</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01504831671634399</v>
+        <v>0.01504831671634406</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09602412435083353</v>
+        <v>0.09602412435083341</v>
       </c>
       <c r="I7" t="n">
-        <v>2.557522790730532e-06</v>
+        <v>2.55752279073053e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007872456760607505</v>
+        <v>0.0007872456760607544</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002595514260808192</v>
+        <v>0.002595514260822621</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9548081448828392</v>
+        <v>0.9548081448828366</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -9612,31 +9612,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.691165984208838</v>
+        <v>1.691165984208855</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2907528775809944</v>
+        <v>0.2907528775809946</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01429131165318597</v>
+        <v>0.01429131165318605</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01517516241554106</v>
+        <v>0.01517516241554105</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09748900343220469</v>
+        <v>0.09748900343220464</v>
       </c>
       <c r="I8" t="n">
         <v>2.97108113230803e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009388991736640472</v>
+        <v>0.0009388991736640461</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003178282225146648</v>
+        <v>0.003178282225150087</v>
       </c>
       <c r="L8" t="n">
-        <v>1.269337505602574</v>
+        <v>1.269337505602577</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -9657,31 +9657,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.360872036542468</v>
+        <v>1.360872036542472</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2706547538947168</v>
+        <v>0.2706547538947164</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009478845741656668</v>
+        <v>0.009478845741656687</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01499743736078509</v>
+        <v>0.01499743736078506</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09562146549083483</v>
+        <v>0.0956214654908354</v>
       </c>
       <c r="I9" t="n">
-        <v>2.556987476983514e-06</v>
+        <v>2.556987476983511e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0007833639240951999</v>
+        <v>0.0007833639240951916</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002591079616328627</v>
+        <v>0.002591079616328756</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9667425315557182</v>
+        <v>0.9667425315557143</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -9702,31 +9702,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.187900481781661</v>
+        <v>1.187900481781649</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2553816424388453</v>
+        <v>0.2553816424388451</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0087204263825904</v>
+        <v>0.008720426382590395</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01491385902758963</v>
+        <v>0.01491385902758964</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09423731588101052</v>
+        <v>0.0942373158810105</v>
       </c>
       <c r="I10" t="n">
-        <v>2.372163985516557e-06</v>
+        <v>2.372163985516555e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0007248864303024624</v>
+        <v>0.0007248864303024644</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002363367877618129</v>
+        <v>0.002363367877611753</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8115566095737525</v>
+        <v>0.8115566095737526</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -9826,16 +9826,16 @@
         <v>2.88837818769634</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3186169771741244</v>
+        <v>0.3186169771741251</v>
       </c>
       <c r="F2" t="n">
         <v>0.03621468244334192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01557196564824552</v>
+        <v>0.01557196564824549</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1009667770899313</v>
+        <v>0.1009667770899311</v>
       </c>
       <c r="I2" t="n">
         <v>4.075563172662792e-06</v>
@@ -9868,31 +9868,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.332387449266164</v>
+        <v>2.332387449266168</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3039913892363109</v>
+        <v>0.3039913892363106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02443314372181957</v>
+        <v>0.02443314372181959</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01538132220463726</v>
+        <v>0.01538132220463733</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09950266143646799</v>
+        <v>0.09950266143646809</v>
       </c>
       <c r="I3" t="n">
-        <v>3.590227273927664e-06</v>
+        <v>3.590227273927669e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001112433618232633</v>
+        <v>0.00111243361823263</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003813720819753734</v>
+        <v>0.003813720819757487</v>
       </c>
       <c r="L3" t="n">
-        <v>1.884149186129416</v>
+        <v>1.884149186129417</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -9913,31 +9913,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.050148731896246</v>
+        <v>2.050148731896244</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2927033980521497</v>
+        <v>0.2927033980521493</v>
       </c>
       <c r="F4" t="n">
         <v>0.01533339641248511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01524914431042959</v>
+        <v>0.01524914431042958</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09854457734191194</v>
+        <v>0.09854457734191198</v>
       </c>
       <c r="I4" t="n">
-        <v>3.216532531912033e-06</v>
+        <v>3.216532531912038e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009917168601908375</v>
+        <v>0.0009917168601908393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003398117346378841</v>
+        <v>0.003398117346378847</v>
       </c>
       <c r="L4" t="n">
-        <v>1.623925163101438</v>
+        <v>1.623925163101439</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -9958,25 +9958,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.50244164351363</v>
+        <v>2.502441643513629</v>
       </c>
       <c r="E5" t="n">
         <v>0.2965067861671022</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01996172491239409</v>
+        <v>0.01996172491239408</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01528541971022187</v>
+        <v>0.01528541971022184</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0990493921303197</v>
+        <v>0.09904939213031982</v>
       </c>
       <c r="I5" t="n">
-        <v>3.315461137385448e-06</v>
+        <v>3.315461137385454e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001078867357490454</v>
+        <v>0.001078867357490453</v>
       </c>
       <c r="K5" t="n">
         <v>0.003708296314999622</v>
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.891496333310505</v>
+        <v>1.891496333310506</v>
       </c>
       <c r="E6" t="n">
         <v>0.2820668209050142</v>
@@ -10012,19 +10012,19 @@
         <v>0.01272660826062423</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01512528837100167</v>
+        <v>0.0151252883710017</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09666441312259548</v>
+        <v>0.09666441312259549</v>
       </c>
       <c r="I6" t="n">
-        <v>2.761299622841463e-06</v>
+        <v>2.761299622839766e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008569489994980376</v>
+        <v>0.0008569489994980367</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00285867894652403</v>
+        <v>0.002858678946524017</v>
       </c>
       <c r="L6" t="n">
         <v>1.48119481147123</v>
@@ -10048,31 +10048,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.704752429431985</v>
+        <v>1.704752429431976</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2692748218174132</v>
+        <v>0.2692748218174136</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01130415107891838</v>
+        <v>0.01130415107891832</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01504831671634399</v>
+        <v>0.01504831671634406</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09602412435083353</v>
+        <v>0.09602412435083341</v>
       </c>
       <c r="I7" t="n">
-        <v>2.557522790730532e-06</v>
+        <v>2.55752279073053e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007872456760607505</v>
+        <v>0.0007872456760607544</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002595514260808192</v>
+        <v>0.002595514260822621</v>
       </c>
       <c r="L7" t="n">
-        <v>1.309715696026133</v>
+        <v>1.309715696026128</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -10093,31 +10093,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.231929184564799</v>
+        <v>2.231929184564806</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2907528775809944</v>
+        <v>0.2907528775809946</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01429131165318597</v>
+        <v>0.01429131165318605</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01517516241554106</v>
+        <v>0.01517516241554105</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09748900343220469</v>
+        <v>0.09748900343220464</v>
       </c>
       <c r="I8" t="n">
         <v>2.97108113230803e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009388991736640472</v>
+        <v>0.0009388991736640461</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003178282225146648</v>
+        <v>0.003178282225150087</v>
       </c>
       <c r="L8" t="n">
-        <v>1.810100719109662</v>
+        <v>1.81010071910966</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -10138,31 +10138,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.764973729089966</v>
+        <v>1.764973729089962</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2706547538947168</v>
+        <v>0.2706547538947164</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009478845741656668</v>
+        <v>0.009478845741656687</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01499743736078509</v>
+        <v>0.01499743736078506</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09562146549083483</v>
+        <v>0.0956214654908354</v>
       </c>
       <c r="I9" t="n">
-        <v>2.556987476983514e-06</v>
+        <v>2.556987476983511e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0007833639240951999</v>
+        <v>0.0007833639240951916</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002591079616328627</v>
+        <v>0.002591079616328756</v>
       </c>
       <c r="L9" t="n">
-        <v>1.370844224103209</v>
+        <v>1.370844224103205</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -10183,31 +10183,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.592773221425427</v>
+        <v>1.592773221425418</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2553816424388453</v>
+        <v>0.2553816424388451</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0087204263825904</v>
+        <v>0.008720426382590395</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01491385902758963</v>
+        <v>0.01491385902758964</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09423731588101052</v>
+        <v>0.0942373158810105</v>
       </c>
       <c r="I10" t="n">
-        <v>2.372163985516557e-06</v>
+        <v>2.372163985516555e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0007248864303024624</v>
+        <v>0.0007248864303024644</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002363367877618129</v>
+        <v>0.002363367877611753</v>
       </c>
       <c r="L10" t="n">
-        <v>1.216429349217521</v>
+        <v>1.216429349217518</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
